--- a/3. outputs/Stock-recruit data/Barkley_Sockeye_stock-recruit_infilled.xlsx
+++ b/3. outputs/Stock-recruit data/Barkley_Sockeye_stock-recruit_infilled.xlsx
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q150"/>
+  <dimension ref="A1:Q153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2765,6 +2765,9 @@
       <c r="L44">
         <v>1</v>
       </c>
+      <c r="N44">
+        <v>328437.0649258933</v>
+      </c>
       <c r="P44">
         <v>0.05</v>
       </c>
@@ -3004,59 +3007,53 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>1972</v>
+        <v>2025</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C50">
-        <v>3500</v>
+        <v>447617</v>
       </c>
       <c r="D50">
-        <v>3500</v>
+        <v>347988</v>
       </c>
       <c r="E50">
-        <v>4407</v>
+        <v>681226</v>
       </c>
       <c r="F50">
-        <v>907</v>
+        <v>233609</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>0.1422831776825899</v>
       </c>
       <c r="H50">
-        <v>0.91</v>
+        <v>0.5630334132872203</v>
       </c>
       <c r="I50">
-        <v>0.06999999999999999</v>
+        <v>0.289163948528095</v>
       </c>
       <c r="J50">
-        <v>0.02</v>
+        <v>0.005519460502094752</v>
       </c>
       <c r="K50">
-        <v>43</v>
+        <v>3262</v>
       </c>
       <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>15100.33608247423</v>
+        <v>1</v>
       </c>
       <c r="P50">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3064,31 +3061,31 @@
         </is>
       </c>
       <c r="C51">
-        <v>40000</v>
+        <v>3500</v>
       </c>
       <c r="D51">
-        <v>40000</v>
+        <v>3500</v>
       </c>
       <c r="E51">
-        <v>58495</v>
+        <v>4407</v>
       </c>
       <c r="F51">
-        <v>18495</v>
+        <v>907</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="I51">
-        <v>0.34</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K51">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -3097,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="N51">
-        <v>30906.24950495049</v>
+        <v>15100.33608247423</v>
       </c>
       <c r="P51">
         <v>0.25</v>
@@ -3108,7 +3105,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3116,31 +3113,31 @@
         </is>
       </c>
       <c r="C52">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="D52">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="E52">
-        <v>8936</v>
+        <v>58495</v>
       </c>
       <c r="F52">
-        <v>2936</v>
+        <v>18495</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="I52">
-        <v>0.43</v>
+        <v>0.34</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -3149,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="N52">
-        <v>23668.15049504951</v>
+        <v>30906.24950495049</v>
       </c>
       <c r="P52">
         <v>0.25</v>
@@ -3160,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3168,31 +3165,31 @@
         </is>
       </c>
       <c r="C53">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="D53">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="E53">
-        <v>17635</v>
+        <v>8936</v>
       </c>
       <c r="F53">
-        <v>7635</v>
+        <v>2936</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0.5742574257425742</v>
+        <v>0.57</v>
       </c>
       <c r="I53">
-        <v>0.4158415841584159</v>
+        <v>0.43</v>
       </c>
       <c r="J53">
-        <v>0.009900990099009901</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -3201,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="N53">
-        <v>153237.7705882353</v>
+        <v>23668.15049504951</v>
       </c>
       <c r="P53">
         <v>0.25</v>
@@ -3212,7 +3209,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3220,40 +3217,40 @@
         </is>
       </c>
       <c r="C54">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="D54">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="E54">
-        <v>8825</v>
+        <v>17635</v>
       </c>
       <c r="F54">
-        <v>5325</v>
+        <v>7635</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0.7319587628865979</v>
+        <v>0.5742574257425742</v>
       </c>
       <c r="I54">
-        <v>0.2680412371134021</v>
+        <v>0.4158415841584159</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>0.009900990099009901</v>
       </c>
       <c r="K54">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
       <c r="N54">
-        <v>127138.0294117647</v>
+        <v>153237.7705882353</v>
       </c>
       <c r="P54">
         <v>0.25</v>
@@ -3264,7 +3261,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3272,31 +3269,31 @@
         </is>
       </c>
       <c r="C55">
-        <v>4800</v>
+        <v>3500</v>
       </c>
       <c r="D55">
-        <v>4800</v>
+        <v>3500</v>
       </c>
       <c r="E55">
-        <v>30860</v>
+        <v>8825</v>
       </c>
       <c r="F55">
-        <v>26060</v>
+        <v>5325</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0.72</v>
+        <v>0.7319587628865979</v>
       </c>
       <c r="I55">
-        <v>0.28</v>
+        <v>0.2680412371134021</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="L55">
         <v>1</v>
@@ -3305,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="N55">
-        <v>120962.5</v>
+        <v>127138.0294117647</v>
       </c>
       <c r="P55">
         <v>0.25</v>
@@ -3316,7 +3313,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3324,31 +3321,31 @@
         </is>
       </c>
       <c r="C56">
-        <v>7000</v>
+        <v>4800</v>
       </c>
       <c r="D56">
-        <v>7000</v>
+        <v>4800</v>
       </c>
       <c r="E56">
-        <v>10832</v>
+        <v>30860</v>
       </c>
       <c r="F56">
-        <v>3832</v>
+        <v>26060</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0.198019801980198</v>
+        <v>0.72</v>
       </c>
       <c r="I56">
-        <v>0.801980198019802</v>
+        <v>0.28</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -3357,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="N56">
-        <v>44237.05555555555</v>
+        <v>120962.5</v>
       </c>
       <c r="P56">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q56">
         <v>1</v>
@@ -3368,7 +3365,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3376,31 +3373,31 @@
         </is>
       </c>
       <c r="C57">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="D57">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="E57">
-        <v>143488</v>
+        <v>10832</v>
       </c>
       <c r="F57">
-        <v>123488</v>
+        <v>3832</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>0.85</v>
+        <v>0.198019801980198</v>
       </c>
       <c r="I57">
-        <v>0.15</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -3409,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="N57">
-        <v>55570.94949494949</v>
+        <v>44237.05555555555</v>
       </c>
       <c r="P57">
         <v>0.2</v>
@@ -3420,7 +3417,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3428,31 +3425,31 @@
         </is>
       </c>
       <c r="C58">
-        <v>20706</v>
+        <v>20000</v>
       </c>
       <c r="D58">
-        <v>20706</v>
+        <v>20000</v>
       </c>
       <c r="E58">
-        <v>67869</v>
+        <v>143488</v>
       </c>
       <c r="F58">
-        <v>47163</v>
+        <v>123488</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>0.5392156862745099</v>
+        <v>0.85</v>
       </c>
       <c r="I58">
-        <v>0.4607843137254902</v>
+        <v>0.15</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="L58">
         <v>1</v>
@@ -3461,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <v>43470.02494949495</v>
+        <v>55570.94949494949</v>
       </c>
       <c r="P58">
         <v>0.2</v>
@@ -3472,7 +3469,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3480,31 +3477,31 @@
         </is>
       </c>
       <c r="C59">
-        <v>58000</v>
+        <v>20706</v>
       </c>
       <c r="D59">
-        <v>58000</v>
+        <v>20706</v>
       </c>
       <c r="E59">
-        <v>175758</v>
+        <v>67869</v>
       </c>
       <c r="F59">
-        <v>117758</v>
+        <v>47163</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>0.4848484848484848</v>
+        <v>0.5392156862745099</v>
       </c>
       <c r="I59">
-        <v>0.5151515151515151</v>
+        <v>0.4607843137254902</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <v>288</v>
+        <v>187</v>
       </c>
       <c r="L59">
         <v>1</v>
@@ -3513,18 +3510,18 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>6318.54</v>
+        <v>43470.02494949495</v>
       </c>
       <c r="P59">
         <v>0.2</v>
       </c>
       <c r="Q59">
-        <v>0.2496267659213876</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3532,31 +3529,31 @@
         </is>
       </c>
       <c r="C60">
-        <v>36700</v>
+        <v>58000</v>
       </c>
       <c r="D60">
-        <v>36700</v>
+        <v>58000</v>
       </c>
       <c r="E60">
-        <v>47662</v>
+        <v>175758</v>
       </c>
       <c r="F60">
-        <v>10962</v>
+        <v>117758</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>0.25</v>
+        <v>0.4848484848484848</v>
       </c>
       <c r="I60">
-        <v>0.75</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="L60">
         <v>1</v>
@@ -3565,18 +3562,18 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>9106.809999999999</v>
+        <v>6318.54</v>
       </c>
       <c r="P60">
         <v>0.2</v>
       </c>
       <c r="Q60">
-        <v>0.2111714885758418</v>
+        <v>0.2496267659213876</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3584,31 +3581,31 @@
         </is>
       </c>
       <c r="C61">
-        <v>31000</v>
+        <v>36700</v>
       </c>
       <c r="D61">
-        <v>30686.86868686869</v>
+        <v>36700</v>
       </c>
       <c r="E61">
-        <v>35227</v>
+        <v>47662</v>
       </c>
       <c r="F61">
-        <v>4227</v>
+        <v>10962</v>
       </c>
       <c r="G61">
-        <v>0.0101010101010101</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0.3232323232323233</v>
+        <v>0.25</v>
       </c>
       <c r="I61">
-        <v>0.6666666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L61">
         <v>1</v>
@@ -3617,18 +3614,18 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>60399.48</v>
+        <v>9106.809999999999</v>
       </c>
       <c r="P61">
         <v>0.2</v>
       </c>
       <c r="Q61">
-        <v>0.2922206205809506</v>
+        <v>0.2111714885758418</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3636,31 +3633,31 @@
         </is>
       </c>
       <c r="C62">
-        <v>73400</v>
+        <v>31000</v>
       </c>
       <c r="D62">
-        <v>73399.99999999999</v>
+        <v>30686.86868686869</v>
       </c>
       <c r="E62">
-        <v>79532</v>
+        <v>35227</v>
       </c>
       <c r="F62">
-        <v>6132</v>
+        <v>4227</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="H62">
-        <v>0.3333333333333333</v>
+        <v>0.3232323232323233</v>
       </c>
       <c r="I62">
-        <v>0.5555555555555555</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J62">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>159</v>
+        <v>293</v>
       </c>
       <c r="L62">
         <v>1</v>
@@ -3669,18 +3666,18 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>28890.6</v>
+        <v>60399.48</v>
       </c>
       <c r="P62">
         <v>0.2</v>
       </c>
       <c r="Q62">
-        <v>0.2565178192417154</v>
+        <v>0.2922206205809506</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3688,31 +3685,31 @@
         </is>
       </c>
       <c r="C63">
-        <v>18500</v>
+        <v>73400</v>
       </c>
       <c r="D63">
-        <v>18500</v>
+        <v>73399.99999999999</v>
       </c>
       <c r="E63">
-        <v>18949</v>
+        <v>79532</v>
       </c>
       <c r="F63">
-        <v>449</v>
+        <v>6132</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>0.13</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I63">
-        <v>0.87</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="K63">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="L63">
         <v>1</v>
@@ -3721,18 +3718,18 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>49682.78747474747</v>
+        <v>28890.6</v>
       </c>
       <c r="P63">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q63">
-        <v>0.2451098642822979</v>
+        <v>0.2565178192417154</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3740,31 +3737,31 @@
         </is>
       </c>
       <c r="C64">
-        <v>3900</v>
+        <v>18500</v>
       </c>
       <c r="D64">
-        <v>3900</v>
+        <v>18500</v>
       </c>
       <c r="E64">
-        <v>3930</v>
+        <v>18949</v>
       </c>
       <c r="F64">
-        <v>30</v>
+        <v>449</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I64">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="J64">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -3773,18 +3770,18 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>20800.80252525253</v>
+        <v>49682.78747474747</v>
       </c>
       <c r="P64">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q64">
-        <v>0.2419729833867256</v>
+        <v>0.2451098642822979</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3792,31 +3789,31 @@
         </is>
       </c>
       <c r="C65">
-        <v>30800</v>
+        <v>3900</v>
       </c>
       <c r="D65">
-        <v>30800</v>
+        <v>3900</v>
       </c>
       <c r="E65">
-        <v>39677</v>
+        <v>3930</v>
       </c>
       <c r="F65">
-        <v>8877</v>
+        <v>30</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65">
-        <v>0.78</v>
+        <v>0.09</v>
       </c>
       <c r="I65">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="J65">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K65">
-        <v>446</v>
+        <v>122</v>
       </c>
       <c r="L65">
         <v>1</v>
@@ -3825,18 +3822,18 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <v>54856.33</v>
+        <v>20800.80252525253</v>
       </c>
       <c r="P65">
         <v>0.2</v>
       </c>
       <c r="Q65">
-        <v>0.2765457477820611</v>
+        <v>0.2419729833867256</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3844,31 +3841,31 @@
         </is>
       </c>
       <c r="C66">
-        <v>40300</v>
+        <v>30800</v>
       </c>
       <c r="D66">
-        <v>40300</v>
+        <v>30800</v>
       </c>
       <c r="E66">
-        <v>42094</v>
+        <v>39677</v>
       </c>
       <c r="F66">
-        <v>1794</v>
+        <v>8877</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0.78</v>
       </c>
       <c r="I66">
-        <v>0.6899999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="J66">
         <v>0.01</v>
       </c>
       <c r="K66">
-        <v>151</v>
+        <v>446</v>
       </c>
       <c r="L66">
         <v>1</v>
@@ -3877,18 +3874,18 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <v>200973.82</v>
+        <v>54856.33</v>
       </c>
       <c r="P66">
         <v>0.2</v>
       </c>
       <c r="Q66">
-        <v>0.231004202683785</v>
+        <v>0.2765457477820611</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3896,31 +3893,31 @@
         </is>
       </c>
       <c r="C67">
-        <v>40600</v>
+        <v>40300</v>
       </c>
       <c r="D67">
-        <v>40600</v>
+        <v>40300</v>
       </c>
       <c r="E67">
-        <v>40656</v>
+        <v>42094</v>
       </c>
       <c r="F67">
-        <v>56</v>
+        <v>1794</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="I67">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J67">
         <v>0.01</v>
       </c>
       <c r="K67">
-        <v>309</v>
+        <v>151</v>
       </c>
       <c r="L67">
         <v>1</v>
@@ -3929,18 +3926,18 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>45367.62</v>
+        <v>200973.82</v>
       </c>
       <c r="P67">
         <v>0.2</v>
       </c>
       <c r="Q67">
-        <v>0.2464772207893425</v>
+        <v>0.231004202683785</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3948,31 +3945,31 @@
         </is>
       </c>
       <c r="C68">
-        <v>31400</v>
+        <v>40600</v>
       </c>
       <c r="D68">
-        <v>31400</v>
+        <v>40600</v>
       </c>
       <c r="E68">
-        <v>32201</v>
+        <v>40656</v>
       </c>
       <c r="F68">
-        <v>801</v>
+        <v>56</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>0.202020202020202</v>
+        <v>0.59</v>
       </c>
       <c r="I68">
-        <v>0.797979797979798</v>
+        <v>0.4</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K68">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L68">
         <v>1</v>
@@ -3981,18 +3978,18 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>39447.62</v>
+        <v>45367.62</v>
       </c>
       <c r="P68">
         <v>0.2</v>
       </c>
       <c r="Q68">
-        <v>0.2480305876316884</v>
+        <v>0.2464772207893425</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4000,31 +3997,31 @@
         </is>
       </c>
       <c r="C69">
-        <v>38100</v>
+        <v>31400</v>
       </c>
       <c r="D69">
-        <v>38100</v>
+        <v>31400</v>
       </c>
       <c r="E69">
-        <v>49295</v>
+        <v>32201</v>
       </c>
       <c r="F69">
-        <v>11195</v>
+        <v>801</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0.71</v>
+        <v>0.202020202020202</v>
       </c>
       <c r="I69">
-        <v>0.29</v>
+        <v>0.797979797979798</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="L69">
         <v>1</v>
@@ -4033,18 +4030,18 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>14078.56927536232</v>
+        <v>39447.62</v>
       </c>
       <c r="P69">
         <v>0.2</v>
       </c>
       <c r="Q69">
-        <v>0.2553852420154066</v>
+        <v>0.2480305876316884</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4052,51 +4049,51 @@
         </is>
       </c>
       <c r="C70">
-        <v>27700</v>
+        <v>38100</v>
       </c>
       <c r="D70">
-        <v>27700</v>
+        <v>38100</v>
       </c>
       <c r="E70">
-        <v>36772</v>
+        <v>49295</v>
       </c>
       <c r="F70">
-        <v>9072</v>
+        <v>11195</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="I70">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="L70">
         <v>1</v>
       </c>
       <c r="M70">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>109194.2223913043</v>
+        <v>14078.56927536232</v>
       </c>
       <c r="P70">
         <v>0.2</v>
       </c>
       <c r="Q70">
-        <v>0.2550631891375683</v>
+        <v>0.2553852420154066</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4104,51 +4101,51 @@
         </is>
       </c>
       <c r="C71">
-        <v>180500</v>
+        <v>27700</v>
       </c>
       <c r="D71">
-        <v>180500</v>
+        <v>27700</v>
       </c>
       <c r="E71">
-        <v>217239</v>
+        <v>36772</v>
       </c>
       <c r="F71">
-        <v>36739</v>
+        <v>9072</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="I71">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="L71">
         <v>1</v>
       </c>
       <c r="M71">
-        <v>659000</v>
+        <v>70000</v>
       </c>
       <c r="N71">
-        <v>113334.7638036304</v>
+        <v>109194.2223913043</v>
       </c>
       <c r="P71">
         <v>0.2</v>
       </c>
       <c r="Q71">
-        <v>0.2553581160154582</v>
+        <v>0.2550631891375683</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4156,51 +4153,51 @@
         </is>
       </c>
       <c r="C72">
-        <v>17400</v>
+        <v>180500</v>
       </c>
       <c r="D72">
-        <v>15834</v>
+        <v>180500</v>
       </c>
       <c r="E72">
-        <v>52598</v>
+        <v>217239</v>
       </c>
       <c r="F72">
-        <v>35198</v>
+        <v>36739</v>
       </c>
       <c r="G72">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0.68</v>
+        <v>0.16</v>
       </c>
       <c r="I72">
-        <v>0.2</v>
+        <v>0.84</v>
       </c>
       <c r="J72">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="L72">
         <v>1</v>
       </c>
       <c r="M72">
-        <v>658000</v>
+        <v>659000</v>
       </c>
       <c r="N72">
-        <v>21002.02876237624</v>
+        <v>113334.7638036304</v>
       </c>
       <c r="P72">
         <v>0.2</v>
       </c>
       <c r="Q72">
-        <v>0.2553220566127163</v>
+        <v>0.2553581160154582</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4208,51 +4205,51 @@
         </is>
       </c>
       <c r="C73">
-        <v>4400</v>
+        <v>17400</v>
       </c>
       <c r="D73">
-        <v>4400</v>
+        <v>15834</v>
       </c>
       <c r="E73">
-        <v>4489</v>
+        <v>52598</v>
       </c>
       <c r="F73">
-        <v>89</v>
+        <v>35198</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H73">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="I73">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="J73">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K73">
-        <v>70</v>
+        <v>254</v>
       </c>
       <c r="L73">
         <v>1</v>
       </c>
       <c r="M73">
-        <v>206000</v>
+        <v>658000</v>
       </c>
       <c r="N73">
-        <v>6103.532659276798</v>
+        <v>21002.02876237624</v>
       </c>
       <c r="P73">
         <v>0.2</v>
       </c>
       <c r="Q73">
-        <v>0.2821999907530116</v>
+        <v>0.2553220566127163</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4260,51 +4257,51 @@
         </is>
       </c>
       <c r="C74">
-        <v>59900</v>
+        <v>4400</v>
       </c>
       <c r="D74">
-        <v>59900</v>
+        <v>4400</v>
       </c>
       <c r="E74">
-        <v>61811</v>
+        <v>4489</v>
       </c>
       <c r="F74">
-        <v>1911</v>
+        <v>89</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74">
-        <v>0.8799209486166009</v>
+        <v>0.16</v>
       </c>
       <c r="I74">
-        <v>0.1200790513833992</v>
+        <v>0.82</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K74">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="L74">
         <v>1</v>
       </c>
       <c r="M74">
-        <v>862000</v>
+        <v>206000</v>
       </c>
       <c r="N74">
-        <v>40080.33552053925</v>
+        <v>6103.532659276798</v>
       </c>
       <c r="P74">
         <v>0.2</v>
       </c>
       <c r="Q74">
-        <v>0.2525725048464748</v>
+        <v>0.2821999907530116</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4312,51 +4309,51 @@
         </is>
       </c>
       <c r="C75">
-        <v>46200</v>
+        <v>59900</v>
       </c>
       <c r="D75">
-        <v>46200</v>
+        <v>59900</v>
       </c>
       <c r="E75">
-        <v>59613</v>
+        <v>61811</v>
       </c>
       <c r="F75">
-        <v>13413</v>
+        <v>1911</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75">
-        <v>0.1111111111111111</v>
+        <v>0.8799209486166009</v>
       </c>
       <c r="I75">
-        <v>0.8686868686868686</v>
+        <v>0.1200790513833992</v>
       </c>
       <c r="J75">
-        <v>0.0202020202020202</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="L75">
         <v>1</v>
       </c>
       <c r="M75">
-        <v>1025000</v>
+        <v>862000</v>
       </c>
       <c r="N75">
-        <v>19458.13390432388</v>
+        <v>40080.33552053925</v>
       </c>
       <c r="P75">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="Q75">
-        <v>0.178692682150781</v>
+        <v>0.2525725048464748</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4364,48 +4361,51 @@
         </is>
       </c>
       <c r="C76">
-        <v>92100</v>
+        <v>46200</v>
       </c>
       <c r="D76">
-        <v>91819.1456043956</v>
+        <v>46200</v>
       </c>
       <c r="E76">
-        <v>119301</v>
+        <v>59613</v>
       </c>
       <c r="F76">
-        <v>27201</v>
+        <v>13413</v>
       </c>
       <c r="G76">
-        <v>0.00304945054945055</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>0.08815018315018315</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I76">
-        <v>0.8834829059829059</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="J76">
-        <v>0.02531746031746032</v>
+        <v>0.0202020202020202</v>
       </c>
       <c r="K76">
-        <v>364</v>
+        <v>97</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76">
-        <v>860000</v>
+        <v>1025000</v>
+      </c>
+      <c r="N76">
+        <v>19458.13390432388</v>
       </c>
       <c r="P76">
         <v>0.15</v>
       </c>
       <c r="Q76">
-        <v>0.2562130945777705</v>
+        <v>0.178692682150781</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4413,48 +4413,48 @@
         </is>
       </c>
       <c r="C77">
-        <v>13400</v>
+        <v>92100</v>
       </c>
       <c r="D77">
-        <v>13400</v>
+        <v>91819.1456043956</v>
       </c>
       <c r="E77">
-        <v>14709</v>
+        <v>119301</v>
       </c>
       <c r="F77">
-        <v>1309</v>
+        <v>27201</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>0.00304945054945055</v>
       </c>
       <c r="H77">
-        <v>0.198019801980198</v>
+        <v>0.08815018315018315</v>
       </c>
       <c r="I77">
-        <v>0.7128712871287128</v>
+        <v>0.8834829059829059</v>
       </c>
       <c r="J77">
-        <v>0.0891089108910891</v>
+        <v>0.02531746031746032</v>
       </c>
       <c r="K77">
-        <v>33</v>
+        <v>364</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>1200000</v>
+        <v>860000</v>
       </c>
       <c r="P77">
         <v>0.15</v>
       </c>
       <c r="Q77">
-        <v>0.2620673654633024</v>
+        <v>0.2562130945777705</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4462,48 +4462,48 @@
         </is>
       </c>
       <c r="C78">
-        <v>25100</v>
+        <v>13400</v>
       </c>
       <c r="D78">
-        <v>25100</v>
+        <v>13400</v>
       </c>
       <c r="E78">
-        <v>25354</v>
+        <v>14709</v>
       </c>
       <c r="F78">
-        <v>254</v>
+        <v>1309</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>0.92</v>
+        <v>0.198019801980198</v>
       </c>
       <c r="I78">
-        <v>0.08</v>
+        <v>0.7128712871287128</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>0.0891089108910891</v>
       </c>
       <c r="K78">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78">
-        <v>1900000</v>
+        <v>1200000</v>
       </c>
       <c r="P78">
         <v>0.15</v>
       </c>
       <c r="Q78">
-        <v>0.2450461298290044</v>
+        <v>0.2620673654633024</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4511,48 +4511,48 @@
         </is>
       </c>
       <c r="C79">
-        <v>19900</v>
+        <v>25100</v>
       </c>
       <c r="D79">
-        <v>19900</v>
+        <v>25100</v>
       </c>
       <c r="E79">
-        <v>21940</v>
+        <v>25354</v>
       </c>
       <c r="F79">
-        <v>2040</v>
+        <v>254</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>0.2841842445114077</v>
+        <v>0.92</v>
       </c>
       <c r="I79">
-        <v>0.6794102453723634</v>
+        <v>0.08</v>
       </c>
       <c r="J79">
-        <v>0.03640551011622901</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="P79">
         <v>0.15</v>
       </c>
       <c r="Q79">
-        <v>0.5</v>
+        <v>0.2450461298290044</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4560,37 +4560,37 @@
         </is>
       </c>
       <c r="C80">
-        <v>17700</v>
+        <v>19900</v>
       </c>
       <c r="D80">
-        <v>17700</v>
+        <v>19900</v>
       </c>
       <c r="E80">
-        <v>21612</v>
+        <v>21940</v>
       </c>
       <c r="F80">
-        <v>3912</v>
+        <v>2040</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>0.3026315789</v>
+        <v>0.2841842445114077</v>
       </c>
       <c r="I80">
-        <v>0.6118421052999999</v>
+        <v>0.6794102453723634</v>
       </c>
       <c r="J80">
-        <v>0.0855263158</v>
+        <v>0.03640551011622901</v>
       </c>
       <c r="K80">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80">
-        <v>2300000</v>
+        <v>2100000</v>
       </c>
       <c r="P80">
         <v>0.15</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4609,40 +4609,37 @@
         </is>
       </c>
       <c r="C81">
-        <v>3300</v>
+        <v>17700</v>
       </c>
       <c r="D81">
-        <v>3300</v>
+        <v>17700</v>
       </c>
       <c r="E81">
-        <v>3537</v>
+        <v>21612</v>
       </c>
       <c r="F81">
-        <v>237</v>
+        <v>3912</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>0.42202</v>
+        <v>0.3026315789</v>
       </c>
       <c r="I81">
-        <v>0.5779799999999999</v>
+        <v>0.6118421052999999</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>0.0855263158</v>
       </c>
       <c r="K81">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81">
-        <v>783000</v>
-      </c>
-      <c r="N81">
-        <v>4464.647292102407</v>
+        <v>2300000</v>
       </c>
       <c r="P81">
         <v>0.15</v>
@@ -4653,7 +4650,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -4661,25 +4658,40 @@
         </is>
       </c>
       <c r="C82">
-        <v>2600</v>
+        <v>3300</v>
+      </c>
+      <c r="D82">
+        <v>3300</v>
       </c>
       <c r="E82">
-        <v>2610</v>
+        <v>3537</v>
       </c>
       <c r="F82">
-        <v>10</v>
+        <v>237</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0.42202</v>
+      </c>
+      <c r="I82">
+        <v>0.5779799999999999</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82">
-        <v>755300</v>
+        <v>783000</v>
       </c>
       <c r="N82">
-        <v>24967.82729054477</v>
+        <v>4463.788101820499</v>
       </c>
       <c r="P82">
         <v>0.15</v>
@@ -4690,7 +4702,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4698,13 +4710,13 @@
         </is>
       </c>
       <c r="C83">
-        <v>1300</v>
+        <v>2600</v>
       </c>
       <c r="E83">
-        <v>1601</v>
+        <v>2610</v>
       </c>
       <c r="F83">
-        <v>301</v>
+        <v>10</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -4713,10 +4725,10 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>97750</v>
+        <v>755300</v>
       </c>
       <c r="N83">
-        <v>26458.95040901615</v>
+        <v>24913.27279902591</v>
       </c>
       <c r="P83">
         <v>0.15</v>
@@ -4727,7 +4739,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4735,13 +4747,13 @@
         </is>
       </c>
       <c r="C84">
-        <v>3600</v>
+        <v>1300</v>
       </c>
       <c r="E84">
-        <v>3897</v>
+        <v>1601</v>
       </c>
       <c r="F84">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -4750,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>1558240</v>
+        <v>97750</v>
       </c>
       <c r="N84">
-        <v>76583.93285522016</v>
+        <v>26368.81550920557</v>
       </c>
       <c r="P84">
         <v>0.15</v>
@@ -4764,7 +4776,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4772,51 +4784,36 @@
         </is>
       </c>
       <c r="C85">
-        <v>12500</v>
-      </c>
-      <c r="D85">
-        <v>12500</v>
+        <v>3600</v>
       </c>
       <c r="E85">
-        <v>12781</v>
+        <v>3897</v>
       </c>
       <c r="F85">
-        <v>281</v>
-      </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>0.04221824310090583</v>
-      </c>
-      <c r="I85">
-        <v>0.946616810617232</v>
-      </c>
-      <c r="J85">
-        <v>0.01116494628186223</v>
+        <v>297</v>
       </c>
       <c r="K85">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>1558240</v>
       </c>
       <c r="N85">
-        <v>14329.98823621049</v>
+        <v>76368.20998018688</v>
       </c>
       <c r="P85">
         <v>0.15</v>
       </c>
       <c r="Q85">
-        <v>0.2487218717321054</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4824,51 +4821,51 @@
         </is>
       </c>
       <c r="C86">
-        <v>13100</v>
+        <v>12500</v>
       </c>
       <c r="D86">
-        <v>12314</v>
+        <v>12500</v>
       </c>
       <c r="E86">
-        <v>13100</v>
+        <v>12781</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="G86">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0.66</v>
+        <v>0.04221824310090583</v>
       </c>
       <c r="I86">
-        <v>0.28</v>
+        <v>0.946616810617232</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>0.01116494628186223</v>
       </c>
       <c r="K86">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86">
         <v>0</v>
       </c>
       <c r="N86">
-        <v>17385.5835483871</v>
+        <v>14327.56678138281</v>
       </c>
       <c r="P86">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="Q86">
-        <v>0.1827938490156061</v>
+        <v>0.2487218717321054</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4876,31 +4873,31 @@
         </is>
       </c>
       <c r="C87">
-        <v>30000</v>
+        <v>13100</v>
       </c>
       <c r="D87">
-        <v>29362.37623762376</v>
+        <v>12314</v>
       </c>
       <c r="E87">
-        <v>37089.49804286085</v>
+        <v>13100</v>
       </c>
       <c r="F87">
-        <v>7089.498042860854</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>0.02125412541254126</v>
+        <v>0.06</v>
       </c>
       <c r="H87">
-        <v>0.5317491749174917</v>
+        <v>0.66</v>
       </c>
       <c r="I87">
-        <v>0.4400660066006601</v>
+        <v>0.28</v>
       </c>
       <c r="J87">
-        <v>0.00693069306930693</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>303</v>
+        <v>52</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -4909,21 +4906,18 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <v>34386.77385321101</v>
-      </c>
-      <c r="O87">
-        <v>0.1911456993747445</v>
+        <v>17385.5835483871</v>
       </c>
       <c r="P87">
-        <v>0.4448298647202095</v>
+        <v>0.2</v>
       </c>
       <c r="Q87">
-        <v>0.5</v>
+        <v>0.1827938490156061</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4934,28 +4928,28 @@
         <v>30000</v>
       </c>
       <c r="D88">
-        <v>29696.9696969697</v>
+        <v>29362.37623762376</v>
       </c>
       <c r="E88">
-        <v>58911.34022354753</v>
+        <v>36965.52915932841</v>
       </c>
       <c r="F88">
-        <v>28911.34022354753</v>
+        <v>6965.529159328415</v>
       </c>
       <c r="G88">
-        <v>0.0101010101010101</v>
+        <v>0.02125412541254126</v>
       </c>
       <c r="H88">
-        <v>0.888888888888889</v>
+        <v>0.5317491749174917</v>
       </c>
       <c r="I88">
-        <v>0.101010101010101</v>
+        <v>0.4400660066006601</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>0.00693069306930693</v>
       </c>
       <c r="K88">
-        <v>67</v>
+        <v>303</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -4964,13 +4958,13 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>8643.726146788991</v>
+        <v>34386.77385321101</v>
       </c>
       <c r="O88">
-        <v>0.4907601849463839</v>
+        <v>0.1884330974759124</v>
       </c>
       <c r="P88">
-        <v>0.4448298647202095</v>
+        <v>0.4362144414764024</v>
       </c>
       <c r="Q88">
         <v>0.5</v>
@@ -4978,7 +4972,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4986,31 +4980,31 @@
         </is>
       </c>
       <c r="C89">
-        <v>20423</v>
+        <v>30000</v>
       </c>
       <c r="D89">
-        <v>20057.36241935484</v>
+        <v>29696.9696969697</v>
       </c>
       <c r="E89">
-        <v>27388</v>
+        <v>58671.61619560767</v>
       </c>
       <c r="F89">
-        <v>6965</v>
+        <v>28671.61619560767</v>
       </c>
       <c r="G89">
-        <v>0.01790322580645161</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="H89">
-        <v>0.1266129032258065</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="I89">
-        <v>0.8554838709677419</v>
+        <v>0.101010101010101</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -5019,18 +5013,21 @@
         <v>0</v>
       </c>
       <c r="N89">
-        <v>43839.87877920145</v>
+        <v>8643.726146788991</v>
+      </c>
+      <c r="O89">
+        <v>0.4886795021977614</v>
       </c>
       <c r="P89">
-        <v>0.07000000000000001</v>
+        <v>0.4362144414764024</v>
       </c>
       <c r="Q89">
-        <v>0.1276418702964884</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5038,31 +5035,31 @@
         </is>
       </c>
       <c r="C90">
-        <v>17133</v>
+        <v>20423</v>
       </c>
       <c r="D90">
-        <v>17133</v>
+        <v>20057.36241935484</v>
       </c>
       <c r="E90">
-        <v>23075</v>
+        <v>27388</v>
       </c>
       <c r="F90">
-        <v>5942</v>
+        <v>6965</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>0.01790322580645161</v>
       </c>
       <c r="H90">
-        <v>0.62</v>
+        <v>0.1266129032258065</v>
       </c>
       <c r="I90">
-        <v>0.38</v>
+        <v>0.8554838709677419</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -5071,18 +5068,18 @@
         <v>0</v>
       </c>
       <c r="N90">
-        <v>10937.88288746522</v>
+        <v>43839.87877920145</v>
       </c>
       <c r="P90">
         <v>0.07000000000000001</v>
       </c>
       <c r="Q90">
-        <v>0.2288747452863037</v>
+        <v>0.1276418702964884</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5090,31 +5087,31 @@
         </is>
       </c>
       <c r="C91">
-        <v>12500</v>
+        <v>17133</v>
       </c>
       <c r="D91">
-        <v>12125</v>
+        <v>17133</v>
       </c>
       <c r="E91">
-        <v>13625</v>
+        <v>23075</v>
       </c>
       <c r="F91">
-        <v>1125</v>
+        <v>5942</v>
       </c>
       <c r="G91">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="I91">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="J91">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -5123,18 +5120,18 @@
         <v>0</v>
       </c>
       <c r="N91">
-        <v>26414.05275956284</v>
+        <v>10937.88288746522</v>
       </c>
       <c r="P91">
         <v>0.07000000000000001</v>
       </c>
       <c r="Q91">
-        <v>0.2903052391163663</v>
+        <v>0.2288747452863037</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5142,31 +5139,31 @@
         </is>
       </c>
       <c r="C92">
-        <v>11837</v>
+        <v>12500</v>
       </c>
       <c r="D92">
-        <v>11837</v>
+        <v>12125</v>
       </c>
       <c r="E92">
-        <v>33493</v>
+        <v>13625</v>
       </c>
       <c r="F92">
-        <v>21656</v>
+        <v>1125</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H92">
-        <v>0.2458715596330275</v>
+        <v>0.67</v>
       </c>
       <c r="I92">
-        <v>0.7541284403669724</v>
+        <v>0.19</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="K92">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -5175,18 +5172,18 @@
         <v>0</v>
       </c>
       <c r="N92">
-        <v>17167.38557377049</v>
+        <v>26414.05275956284</v>
       </c>
       <c r="P92">
         <v>0.07000000000000001</v>
       </c>
       <c r="Q92">
-        <v>0.2556215086392382</v>
+        <v>0.2903052391163663</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5194,31 +5191,31 @@
         </is>
       </c>
       <c r="C93">
-        <v>6400</v>
+        <v>11837</v>
       </c>
       <c r="D93">
-        <v>6400</v>
+        <v>11837</v>
       </c>
       <c r="E93">
-        <v>11592</v>
+        <v>33493</v>
       </c>
       <c r="F93">
-        <v>5192</v>
+        <v>21656</v>
       </c>
       <c r="G93">
         <v>0</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0.2458715596330275</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>0.7541284403669724</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -5227,18 +5224,18 @@
         <v>0</v>
       </c>
       <c r="N93">
-        <v>1239.474074074074</v>
+        <v>17167.38557377049</v>
       </c>
       <c r="P93">
         <v>0.07000000000000001</v>
       </c>
       <c r="Q93">
-        <v>0.241441424039182</v>
+        <v>0.2556215086392382</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5246,31 +5243,31 @@
         </is>
       </c>
       <c r="C94">
-        <v>10700</v>
+        <v>6400</v>
       </c>
       <c r="D94">
-        <v>10700</v>
+        <v>6400</v>
       </c>
       <c r="E94">
-        <v>33811</v>
+        <v>11592</v>
       </c>
       <c r="F94">
-        <v>23111</v>
+        <v>5192</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>0.06965637740244612</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>0.9303436225975539</v>
+        <v>0</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -5279,18 +5276,18 @@
         <v>0</v>
       </c>
       <c r="N94">
-        <v>6640.959620596205</v>
+        <v>1239.474074074074</v>
       </c>
       <c r="P94">
         <v>0.07000000000000001</v>
       </c>
       <c r="Q94">
-        <v>0.2497769802817572</v>
+        <v>0.241441424039182</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5298,31 +5295,31 @@
         </is>
       </c>
       <c r="C95">
-        <v>22704</v>
+        <v>10700</v>
       </c>
       <c r="D95">
-        <v>22704</v>
+        <v>10700</v>
       </c>
       <c r="E95">
-        <v>25921</v>
+        <v>33811</v>
       </c>
       <c r="F95">
-        <v>3217</v>
+        <v>23111</v>
       </c>
       <c r="G95">
         <v>0</v>
       </c>
       <c r="H95">
-        <v>0.6383333333333332</v>
+        <v>0.06965637740244612</v>
       </c>
       <c r="I95">
-        <v>0.3311111111111111</v>
+        <v>0.9303436225975539</v>
       </c>
       <c r="J95">
-        <v>0.03055555555555556</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -5331,18 +5328,18 @@
         <v>0</v>
       </c>
       <c r="N95">
-        <v>32845.64926303271</v>
+        <v>6640.959620596205</v>
       </c>
       <c r="P95">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q95">
-        <v>0.2440455592874953</v>
+        <v>0.2497769802817572</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5350,31 +5347,31 @@
         </is>
       </c>
       <c r="C96">
-        <v>12203</v>
+        <v>22704</v>
       </c>
       <c r="D96">
-        <v>12203</v>
+        <v>22704</v>
       </c>
       <c r="E96">
-        <v>12829</v>
+        <v>25921</v>
       </c>
       <c r="F96">
-        <v>626</v>
+        <v>3217</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>0.2308196721311475</v>
+        <v>0.6383333333333332</v>
       </c>
       <c r="I96">
-        <v>0.7691803278688525</v>
+        <v>0.3311111111111111</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>0.03055555555555556</v>
       </c>
       <c r="K96">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -5383,18 +5380,18 @@
         <v>0</v>
       </c>
       <c r="N96">
-        <v>26186.83729546156</v>
+        <v>32845.64926303271</v>
       </c>
       <c r="P96">
         <v>0.05</v>
       </c>
       <c r="Q96">
-        <v>0.2425905410682488</v>
+        <v>0.2440455592874953</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5402,48 +5399,51 @@
         </is>
       </c>
       <c r="C97">
-        <v>13549</v>
+        <v>12203</v>
       </c>
       <c r="D97">
-        <v>13549</v>
+        <v>12203</v>
       </c>
       <c r="E97">
-        <v>13703</v>
+        <v>12829</v>
       </c>
       <c r="F97">
-        <v>154</v>
+        <v>626</v>
       </c>
       <c r="G97">
         <v>0</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>0.2308196721311475</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>0.7691803278688525</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97">
         <v>0</v>
+      </c>
+      <c r="N97">
+        <v>26186.83729546156</v>
       </c>
       <c r="P97">
         <v>0.05</v>
       </c>
       <c r="Q97">
-        <v>0.2388851566095718</v>
+        <v>0.2425905410682488</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5451,48 +5451,51 @@
         </is>
       </c>
       <c r="C98">
-        <v>4589</v>
+        <v>13549</v>
       </c>
       <c r="D98">
-        <v>4588.999999999999</v>
+        <v>13549</v>
       </c>
       <c r="E98">
-        <v>5032</v>
+        <v>13703</v>
       </c>
       <c r="F98">
-        <v>443</v>
+        <v>154</v>
       </c>
       <c r="G98">
         <v>0</v>
       </c>
       <c r="H98">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I98">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J98">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K98">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98">
         <v>0</v>
+      </c>
+      <c r="N98">
+        <v>9745.879746835442</v>
       </c>
       <c r="P98">
         <v>0.05</v>
       </c>
       <c r="Q98">
-        <v>0.2506997776881581</v>
+        <v>0.2388851566095718</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5500,31 +5503,31 @@
         </is>
       </c>
       <c r="C99">
-        <v>14520</v>
+        <v>4589</v>
       </c>
       <c r="D99">
-        <v>14520</v>
+        <v>4588.999999999999</v>
       </c>
       <c r="E99">
-        <v>18879</v>
+        <v>5032</v>
       </c>
       <c r="F99">
-        <v>4359</v>
+        <v>443</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>0.8395061728395061</v>
+        <v>0.7</v>
       </c>
       <c r="I99">
-        <v>0.1481481481481481</v>
+        <v>0.2</v>
       </c>
       <c r="J99">
-        <v>0.01234567901234568</v>
+        <v>0.1</v>
       </c>
       <c r="K99">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -5536,12 +5539,12 @@
         <v>0.05</v>
       </c>
       <c r="Q99">
-        <v>0.1397559218405289</v>
+        <v>0.2506997776881581</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -5549,31 +5552,31 @@
         </is>
       </c>
       <c r="C100">
-        <v>18646</v>
+        <v>14520</v>
       </c>
       <c r="D100">
-        <v>18646</v>
+        <v>14520</v>
       </c>
       <c r="E100">
-        <v>26377</v>
+        <v>18879</v>
       </c>
       <c r="F100">
-        <v>7731</v>
+        <v>4359</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>0.3536585365853658</v>
+        <v>0.8395061728395061</v>
       </c>
       <c r="I100">
-        <v>0.6341463414634146</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="J100">
-        <v>0.01219512195121951</v>
+        <v>0.01234567901234568</v>
       </c>
       <c r="K100">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -5585,12 +5588,12 @@
         <v>0.05</v>
       </c>
       <c r="Q100">
-        <v>0.1759984840093463</v>
+        <v>0.1397559218405289</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -5598,31 +5601,31 @@
         </is>
       </c>
       <c r="C101">
-        <v>13113</v>
+        <v>18646</v>
       </c>
       <c r="D101">
-        <v>13113</v>
+        <v>18646</v>
       </c>
       <c r="E101">
-        <v>21309</v>
+        <v>26377</v>
       </c>
       <c r="F101">
-        <v>8196</v>
+        <v>7731</v>
       </c>
       <c r="G101">
         <v>0</v>
       </c>
       <c r="H101">
-        <v>0.1962025316455696</v>
+        <v>0.3536585365853658</v>
       </c>
       <c r="I101">
-        <v>0.7911392405063291</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="J101">
-        <v>0.01265822784810127</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="K101">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -5634,12 +5637,12 @@
         <v>0.05</v>
       </c>
       <c r="Q101">
-        <v>0.1761708452318516</v>
+        <v>0.1759984840093463</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -5647,31 +5650,31 @@
         </is>
       </c>
       <c r="C102">
-        <v>3537</v>
+        <v>13113</v>
       </c>
       <c r="D102">
-        <v>3534.019142788346</v>
+        <v>13113</v>
       </c>
       <c r="E102">
-        <v>8306</v>
+        <v>21309</v>
       </c>
       <c r="F102">
-        <v>4769</v>
+        <v>8196</v>
       </c>
       <c r="G102">
-        <v>0.0008427642667950878</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>0.3291596436311101</v>
+        <v>0.1962025316455696</v>
       </c>
       <c r="I102">
-        <v>0.6699975921020949</v>
+        <v>0.7911392405063291</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="K102">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -5683,110 +5686,110 @@
         <v>0.05</v>
       </c>
       <c r="Q102">
-        <v>0.1677283430730512</v>
+        <v>0.1761708452318516</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>1977</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="C103">
-        <v>80800</v>
+        <v>3537</v>
       </c>
       <c r="D103">
-        <v>76661.99460916442</v>
+        <v>3534.019142788346</v>
       </c>
       <c r="E103">
-        <v>383249.5382626585</v>
+        <v>8306</v>
       </c>
       <c r="F103">
-        <v>302449.5382626585</v>
+        <v>4769</v>
       </c>
       <c r="G103">
-        <v>0.02878880519681817</v>
+        <v>0.0008427642667950878</v>
       </c>
       <c r="H103">
-        <v>0.4997318605819395</v>
+        <v>0.3291596436311101</v>
       </c>
       <c r="I103">
-        <v>0.4352700091205077</v>
+        <v>0.6699975921020949</v>
       </c>
       <c r="J103">
-        <v>0.03620932510073455</v>
+        <v>0</v>
       </c>
       <c r="K103">
-        <v>785</v>
+        <v>86</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
-      <c r="N103">
-        <v>495061.8834075385</v>
+      <c r="M103">
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="Q103">
-        <v>0.12</v>
+        <v>0.1677283430730512</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>1978</v>
+        <v>2025</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="C104">
-        <v>37500</v>
+        <v>15964</v>
       </c>
       <c r="D104">
-        <v>34090.90909090909</v>
+        <v>15911.26308229999</v>
       </c>
       <c r="E104">
-        <v>85204.66517691736</v>
+        <v>20887</v>
       </c>
       <c r="F104">
-        <v>47704.66517691736</v>
+        <v>4923</v>
       </c>
       <c r="G104">
-        <v>0.0518113874782236</v>
+        <v>0.003303490209221046</v>
       </c>
       <c r="H104">
-        <v>0.4044291502443838</v>
+        <v>0.9818547421841336</v>
       </c>
       <c r="I104">
-        <v>0.5020406044948234</v>
+        <v>0.01484176760664528</v>
       </c>
       <c r="J104">
-        <v>0.04171885778256935</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>785</v>
+        <v>210</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
-      <c r="N104">
-        <v>552803.0040534479</v>
+      <c r="M104">
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="Q104">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -5794,28 +5797,28 @@
         </is>
       </c>
       <c r="C105">
-        <v>76446</v>
+        <v>80800</v>
       </c>
       <c r="D105">
-        <v>42180.84255319149</v>
+        <v>76661.99460916442</v>
       </c>
       <c r="E105">
-        <v>233094.7207437111</v>
+        <v>383249.5382626585</v>
       </c>
       <c r="F105">
-        <v>156648.7207437111</v>
+        <v>302449.5382626585</v>
       </c>
       <c r="G105">
-        <v>0.1644626500469068</v>
+        <v>0.02878880519681817</v>
       </c>
       <c r="H105">
-        <v>0.4369388987318761</v>
+        <v>0.4997318605819395</v>
       </c>
       <c r="I105">
-        <v>0.3696527624962592</v>
+        <v>0.4352700091205077</v>
       </c>
       <c r="J105">
-        <v>0.02894568872495793</v>
+        <v>0.03620932510073455</v>
       </c>
       <c r="K105">
         <v>785</v>
@@ -5824,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="N105">
-        <v>570766.8540090187</v>
+        <v>495061.8834075385</v>
       </c>
       <c r="P105">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Q105">
         <v>0.12</v>
@@ -5835,7 +5838,7 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -5843,37 +5846,37 @@
         </is>
       </c>
       <c r="C106">
-        <v>137990</v>
+        <v>37500</v>
       </c>
       <c r="D106">
-        <v>124942.5340393344</v>
+        <v>34090.90909090909</v>
       </c>
       <c r="E106">
-        <v>364922.9973691748</v>
+        <v>85204.66517691736</v>
       </c>
       <c r="F106">
-        <v>226932.9973691748</v>
+        <v>47704.66517691736</v>
       </c>
       <c r="G106">
-        <v>0.04797835692885812</v>
+        <v>0.0518113874782236</v>
       </c>
       <c r="H106">
-        <v>0.5604347519103617</v>
+        <v>0.4044291502443838</v>
       </c>
       <c r="I106">
-        <v>0.3639261125234763</v>
+        <v>0.5020406044948234</v>
       </c>
       <c r="J106">
-        <v>0.02766077863730382</v>
+        <v>0.04171885778256935</v>
       </c>
       <c r="K106">
-        <v>865</v>
+        <v>785</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="N106">
-        <v>391376.4267260354</v>
+        <v>552803.0040534479</v>
       </c>
       <c r="P106">
         <v>0.2</v>
@@ -5884,7 +5887,7 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -5892,37 +5895,37 @@
         </is>
       </c>
       <c r="C107">
-        <v>139251</v>
+        <v>76446</v>
       </c>
       <c r="D107">
-        <v>118709.6861063465</v>
+        <v>42180.84255319149</v>
       </c>
       <c r="E107">
-        <v>502829.9293237749</v>
+        <v>233094.7207437111</v>
       </c>
       <c r="F107">
-        <v>363578.9293237749</v>
+        <v>156648.7207437111</v>
       </c>
       <c r="G107">
-        <v>0.05332893550796541</v>
+        <v>0.1644626500469068</v>
       </c>
       <c r="H107">
-        <v>0.4871769609570211</v>
+        <v>0.4369388987318761</v>
       </c>
       <c r="I107">
-        <v>0.4264518669396213</v>
+        <v>0.3696527624962592</v>
       </c>
       <c r="J107">
-        <v>0.03304223659539225</v>
+        <v>0.02894568872495793</v>
       </c>
       <c r="K107">
-        <v>982</v>
+        <v>785</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
       <c r="N107">
-        <v>288014.3071424381</v>
+        <v>570766.8540090187</v>
       </c>
       <c r="P107">
         <v>0.2</v>
@@ -5933,7 +5936,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -5941,37 +5944,37 @@
         </is>
       </c>
       <c r="C108">
-        <v>248700</v>
+        <v>137990</v>
       </c>
       <c r="D108">
-        <v>213477.4162679426</v>
+        <v>124942.5340393344</v>
       </c>
       <c r="E108">
-        <v>505253.3639629543</v>
+        <v>364922.9973691748</v>
       </c>
       <c r="F108">
-        <v>256553.3639629543</v>
+        <v>226932.9973691748</v>
       </c>
       <c r="G108">
-        <v>0.08221489925215013</v>
+        <v>0.04797835692885812</v>
       </c>
       <c r="H108">
-        <v>0.470630192288445</v>
+        <v>0.5604347519103617</v>
       </c>
       <c r="I108">
-        <v>0.4232998537286816</v>
+        <v>0.3639261125234763</v>
       </c>
       <c r="J108">
-        <v>0.02385505473072335</v>
+        <v>0.02766077863730382</v>
       </c>
       <c r="K108">
-        <v>1031</v>
+        <v>865</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="N108">
-        <v>203184.164250254</v>
+        <v>391376.4267260354</v>
       </c>
       <c r="P108">
         <v>0.2</v>
@@ -5982,7 +5985,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -5990,37 +5993,37 @@
         </is>
       </c>
       <c r="C109">
-        <v>257410</v>
+        <v>139251</v>
       </c>
       <c r="D109">
-        <v>239763.0621572212</v>
+        <v>118709.6861063465</v>
       </c>
       <c r="E109">
-        <v>633080.2506709985</v>
+        <v>502829.9293237749</v>
       </c>
       <c r="F109">
-        <v>375670.2506709985</v>
+        <v>363578.9293237749</v>
       </c>
       <c r="G109">
-        <v>0.03920607812862089</v>
+        <v>0.05332893550796541</v>
       </c>
       <c r="H109">
-        <v>0.5105522297194584</v>
+        <v>0.4871769609570211</v>
       </c>
       <c r="I109">
-        <v>0.420683597959684</v>
+        <v>0.4264518669396213</v>
       </c>
       <c r="J109">
-        <v>0.02955809419223682</v>
+        <v>0.03304223659539225</v>
       </c>
       <c r="K109">
-        <v>881</v>
+        <v>982</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
       <c r="N109">
-        <v>371601.962535504</v>
+        <v>288014.3071424381</v>
       </c>
       <c r="P109">
         <v>0.2</v>
@@ -6031,7 +6034,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -6039,37 +6042,37 @@
         </is>
       </c>
       <c r="C110">
-        <v>89100.00000000001</v>
+        <v>248700</v>
       </c>
       <c r="D110">
-        <v>76373.17581599805</v>
+        <v>213477.4162679426</v>
       </c>
       <c r="E110">
-        <v>510049.2313191415</v>
+        <v>505253.3639629543</v>
       </c>
       <c r="F110">
-        <v>420949.2313191415</v>
+        <v>256553.3639629543</v>
       </c>
       <c r="G110">
-        <v>0.03731300657278514</v>
+        <v>0.08221489925215013</v>
       </c>
       <c r="H110">
-        <v>0.5262929241010506</v>
+        <v>0.470630192288445</v>
       </c>
       <c r="I110">
-        <v>0.3935086920877151</v>
+        <v>0.4232998537286816</v>
       </c>
       <c r="J110">
-        <v>0.04288537723844926</v>
+        <v>0.02385505473072335</v>
       </c>
       <c r="K110">
-        <v>661</v>
+        <v>1031</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
       <c r="N110">
-        <v>340157.6785086803</v>
+        <v>203184.164250254</v>
       </c>
       <c r="P110">
         <v>0.2</v>
@@ -6080,7 +6083,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -6088,40 +6091,40 @@
         </is>
       </c>
       <c r="C111">
-        <v>146951</v>
+        <v>257410</v>
       </c>
       <c r="D111">
-        <v>113688.1031567638</v>
+        <v>239763.0621572212</v>
       </c>
       <c r="E111">
-        <v>286919.9808822382</v>
+        <v>633080.2506709985</v>
       </c>
       <c r="F111">
-        <v>139968.9808822382</v>
+        <v>375670.2506709985</v>
       </c>
       <c r="G111">
-        <v>0.1382341396947662</v>
+        <v>0.03920607812862089</v>
       </c>
       <c r="H111">
-        <v>0.508458040651963</v>
+        <v>0.5105522297194584</v>
       </c>
       <c r="I111">
-        <v>0.3348421830338491</v>
+        <v>0.420683597959684</v>
       </c>
       <c r="J111">
-        <v>0.01846563661942167</v>
+        <v>0.02955809419223682</v>
       </c>
       <c r="K111">
-        <v>237</v>
+        <v>881</v>
       </c>
       <c r="L111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>172160.3662147925</v>
+        <v>371601.962535504</v>
       </c>
       <c r="P111">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q111">
         <v>0.12</v>
@@ -6129,7 +6132,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6137,37 +6140,37 @@
         </is>
       </c>
       <c r="C112">
-        <v>192941</v>
+        <v>89100.00000000001</v>
       </c>
       <c r="D112">
-        <v>173915.3582739309</v>
+        <v>76373.17581599805</v>
       </c>
       <c r="E112">
-        <v>239543.2584870655</v>
+        <v>510049.2313191415</v>
       </c>
       <c r="F112">
-        <v>46602.25848706553</v>
+        <v>420949.2313191415</v>
       </c>
       <c r="G112">
-        <v>0.07016805989850113</v>
+        <v>0.03731300657278514</v>
       </c>
       <c r="H112">
-        <v>0.4187743295557431</v>
+        <v>0.5262929241010506</v>
       </c>
       <c r="I112">
-        <v>0.50250959784696</v>
+        <v>0.3935086920877151</v>
       </c>
       <c r="J112">
-        <v>0.008548012698795749</v>
+        <v>0.04288537723844926</v>
       </c>
       <c r="K112">
-        <v>353</v>
+        <v>661</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
       <c r="N112">
-        <v>265697.028795797</v>
+        <v>340157.6785086803</v>
       </c>
       <c r="P112">
         <v>0.2</v>
@@ -6178,7 +6181,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6186,40 +6189,40 @@
         </is>
       </c>
       <c r="C113">
-        <v>151835</v>
+        <v>146951</v>
       </c>
       <c r="D113">
-        <v>105457.4196508409</v>
+        <v>113688.1031567638</v>
       </c>
       <c r="E113">
-        <v>323200.5978613414</v>
+        <v>286919.9808822382</v>
       </c>
       <c r="F113">
-        <v>171365.5978613414</v>
+        <v>139968.9808822382</v>
       </c>
       <c r="G113">
-        <v>0.2509531374248469</v>
+        <v>0.1382341396947662</v>
       </c>
       <c r="H113">
-        <v>0.5640901338215516</v>
+        <v>0.508458040651963</v>
       </c>
       <c r="I113">
-        <v>0.1765307572447738</v>
+        <v>0.3348421830338491</v>
       </c>
       <c r="J113">
-        <v>0.008425971508827771</v>
+        <v>0.01846563661942167</v>
       </c>
       <c r="K113">
-        <v>785</v>
+        <v>237</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113">
-        <v>652446.9029476116</v>
+        <v>172160.3662147925</v>
       </c>
       <c r="P113">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q113">
         <v>0.12</v>
@@ -6227,7 +6230,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -6235,37 +6238,37 @@
         </is>
       </c>
       <c r="C114">
-        <v>235417</v>
+        <v>192941</v>
       </c>
       <c r="D114">
-        <v>210518.4807253591</v>
+        <v>173915.3582739309</v>
       </c>
       <c r="E114">
-        <v>413687.5671690237</v>
+        <v>239543.2584870655</v>
       </c>
       <c r="F114">
-        <v>178270.5671690237</v>
+        <v>46602.25848706553</v>
       </c>
       <c r="G114">
-        <v>0.06155677181592897</v>
+        <v>0.07016805989850113</v>
       </c>
       <c r="H114">
-        <v>0.535166188018521</v>
+        <v>0.4187743295557431</v>
       </c>
       <c r="I114">
-        <v>0.388404430338482</v>
+        <v>0.50250959784696</v>
       </c>
       <c r="J114">
-        <v>0.01487260982706801</v>
+        <v>0.008548012698795749</v>
       </c>
       <c r="K114">
-        <v>1357</v>
+        <v>353</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>625355.4802804298</v>
+        <v>265697.028795797</v>
       </c>
       <c r="P114">
         <v>0.2</v>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -6284,37 +6287,37 @@
         </is>
       </c>
       <c r="C115">
-        <v>167987</v>
+        <v>151835</v>
       </c>
       <c r="D115">
-        <v>133348.8706677649</v>
+        <v>105457.4196508409</v>
       </c>
       <c r="E115">
-        <v>181390.4704997374</v>
+        <v>323200.5978613414</v>
       </c>
       <c r="F115">
-        <v>13403.47049973736</v>
+        <v>171365.5978613414</v>
       </c>
       <c r="G115">
-        <v>0.1874633738387921</v>
+        <v>0.2509531374248469</v>
       </c>
       <c r="H115">
-        <v>0.548103033321056</v>
+        <v>0.5640901338215516</v>
       </c>
       <c r="I115">
-        <v>0.1993732595713665</v>
+        <v>0.1765307572447738</v>
       </c>
       <c r="J115">
-        <v>0.06506033326878548</v>
+        <v>0.008425971508827771</v>
       </c>
       <c r="K115">
-        <v>699</v>
+        <v>785</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="N115">
-        <v>407468.2247957478</v>
+        <v>652446.9029476116</v>
       </c>
       <c r="P115">
         <v>0.2</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -6333,37 +6336,37 @@
         </is>
       </c>
       <c r="C116">
-        <v>112790</v>
+        <v>235417</v>
       </c>
       <c r="D116">
-        <v>93631.45405437797</v>
+        <v>210518.4807253591</v>
       </c>
       <c r="E116">
-        <v>130025.7962531239</v>
+        <v>413687.5671690237</v>
       </c>
       <c r="F116">
-        <v>17235.79625312389</v>
+        <v>178270.5671690237</v>
       </c>
       <c r="G116">
-        <v>0.1502811798914366</v>
+        <v>0.06155677181592897</v>
       </c>
       <c r="H116">
-        <v>0.5182584503862138</v>
+        <v>0.535166188018521</v>
       </c>
       <c r="I116">
-        <v>0.3199744431630971</v>
+        <v>0.388404430338482</v>
       </c>
       <c r="J116">
-        <v>0.01148592655925249</v>
+        <v>0.01487260982706801</v>
       </c>
       <c r="K116">
-        <v>590</v>
+        <v>1357</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="N116">
-        <v>181984.1898199186</v>
+        <v>625355.4802804298</v>
       </c>
       <c r="P116">
         <v>0.2</v>
@@ -6374,7 +6377,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -6382,37 +6385,37 @@
         </is>
       </c>
       <c r="C117">
-        <v>209475</v>
+        <v>167987</v>
       </c>
       <c r="D117">
-        <v>140122.8844337406</v>
+        <v>133348.8706677649</v>
       </c>
       <c r="E117">
-        <v>572072.5242628852</v>
+        <v>181390.4704997374</v>
       </c>
       <c r="F117">
-        <v>362597.5242628852</v>
+        <v>13403.47049973736</v>
       </c>
       <c r="G117">
-        <v>0.1201522159603099</v>
+        <v>0.1874633738387921</v>
       </c>
       <c r="H117">
-        <v>0.5996406154261705</v>
+        <v>0.548103033321056</v>
       </c>
       <c r="I117">
-        <v>0.2702967185400503</v>
+        <v>0.1993732595713665</v>
       </c>
       <c r="J117">
-        <v>0.009910450073469334</v>
+        <v>0.06506033326878548</v>
       </c>
       <c r="K117">
-        <v>797</v>
+        <v>699</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="N117">
-        <v>59697.7030353223</v>
+        <v>407468.2247957478</v>
       </c>
       <c r="P117">
         <v>0.2</v>
@@ -6423,7 +6426,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -6431,37 +6434,37 @@
         </is>
       </c>
       <c r="C118">
-        <v>221937.9999999999</v>
+        <v>112790</v>
       </c>
       <c r="D118">
-        <v>192641.2435207396</v>
+        <v>93631.45405437797</v>
       </c>
       <c r="E118">
-        <v>614281.3132087174</v>
+        <v>130025.7962531239</v>
       </c>
       <c r="F118">
-        <v>392343.3132087174</v>
+        <v>17235.79625312389</v>
       </c>
       <c r="G118">
-        <v>0.06122716774128441</v>
+        <v>0.1502811798914366</v>
       </c>
       <c r="H118">
-        <v>0.5119032654663909</v>
+        <v>0.5182584503862138</v>
       </c>
       <c r="I118">
-        <v>0.4111167427130682</v>
+        <v>0.3199744431630971</v>
       </c>
       <c r="J118">
-        <v>0.0157528240792566</v>
+        <v>0.01148592655925249</v>
       </c>
       <c r="K118">
-        <v>1839</v>
+        <v>590</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>320116.8393461921</v>
+        <v>181984.1898199186</v>
       </c>
       <c r="P118">
         <v>0.2</v>
@@ -6472,7 +6475,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -6480,37 +6483,37 @@
         </is>
       </c>
       <c r="C119">
-        <v>205289</v>
+        <v>209475</v>
       </c>
       <c r="D119">
-        <v>187859.553457061</v>
+        <v>140122.8844337406</v>
       </c>
       <c r="E119">
-        <v>553495.7834714376</v>
+        <v>572072.5242628852</v>
       </c>
       <c r="F119">
-        <v>348206.7834714376</v>
+        <v>362597.5242628852</v>
       </c>
       <c r="G119">
-        <v>0.04657585274638193</v>
+        <v>0.1201522159603099</v>
       </c>
       <c r="H119">
-        <v>0.4580143339680279</v>
+        <v>0.5996406154261705</v>
       </c>
       <c r="I119">
-        <v>0.4279707814595752</v>
+        <v>0.2702967185400503</v>
       </c>
       <c r="J119">
-        <v>0.06743903182601493</v>
+        <v>0.009910450073469334</v>
       </c>
       <c r="K119">
-        <v>1120</v>
+        <v>797</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>263927.9811106482</v>
+        <v>59697.7030353223</v>
       </c>
       <c r="P119">
         <v>0.2</v>
@@ -6521,7 +6524,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -6529,37 +6532,37 @@
         </is>
       </c>
       <c r="C120">
-        <v>143770.0000000001</v>
+        <v>221937.9999999999</v>
       </c>
       <c r="D120">
-        <v>142161.6046520956</v>
+        <v>192641.2435207396</v>
       </c>
       <c r="E120">
-        <v>225790.0405157967</v>
+        <v>614281.3132087174</v>
       </c>
       <c r="F120">
-        <v>82020.04051579669</v>
+        <v>392343.3132087174</v>
       </c>
       <c r="G120">
-        <v>0.008425690543922759</v>
+        <v>0.06122716774128441</v>
       </c>
       <c r="H120">
-        <v>0.4852898551071586</v>
+        <v>0.5119032654663909</v>
       </c>
       <c r="I120">
-        <v>0.4828686045852089</v>
+        <v>0.4111167427130682</v>
       </c>
       <c r="J120">
-        <v>0.02341584976370976</v>
+        <v>0.0157528240792566</v>
       </c>
       <c r="K120">
-        <v>955</v>
+        <v>1839</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="N120">
-        <v>189096.9567127897</v>
+        <v>320116.8393461921</v>
       </c>
       <c r="P120">
         <v>0.2</v>
@@ -6570,7 +6573,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -6578,37 +6581,37 @@
         </is>
       </c>
       <c r="C121">
-        <v>102400</v>
+        <v>205289</v>
       </c>
       <c r="D121">
-        <v>43254.28652665103</v>
+        <v>187859.553457061</v>
       </c>
       <c r="E121">
-        <v>114921.7067697761</v>
+        <v>553495.7834714376</v>
       </c>
       <c r="F121">
-        <v>12521.70676977609</v>
+        <v>348206.7834714376</v>
       </c>
       <c r="G121">
-        <v>0.481790396233426</v>
+        <v>0.04657585274638193</v>
       </c>
       <c r="H121">
-        <v>0.05911150543870575</v>
+        <v>0.4580143339680279</v>
       </c>
       <c r="I121">
-        <v>0.395388677510043</v>
+        <v>0.4279707814595752</v>
       </c>
       <c r="J121">
-        <v>0.0637094208178252</v>
+        <v>0.06743903182601493</v>
       </c>
       <c r="K121">
-        <v>702</v>
+        <v>1120</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="N121">
-        <v>386548.9231194458</v>
+        <v>263927.9811106482</v>
       </c>
       <c r="P121">
         <v>0.2</v>
@@ -6619,7 +6622,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -6627,48 +6630,48 @@
         </is>
       </c>
       <c r="C122">
-        <v>255498</v>
+        <v>143770.0000000001</v>
       </c>
       <c r="D122">
-        <v>207716.095873672</v>
+        <v>142161.6046520956</v>
       </c>
       <c r="E122">
-        <v>289309.9562418167</v>
+        <v>225790.0405157967</v>
       </c>
       <c r="F122">
-        <v>33811.95624181666</v>
+        <v>82020.04051579669</v>
       </c>
       <c r="G122">
-        <v>0.1432793974269345</v>
+        <v>0.008425690543922759</v>
       </c>
       <c r="H122">
-        <v>0.6826944427680578</v>
+        <v>0.4852898551071586</v>
       </c>
       <c r="I122">
-        <v>0.1699049949987613</v>
+        <v>0.4828686045852089</v>
       </c>
       <c r="J122">
-        <v>0.004121164806246279</v>
+        <v>0.02341584976370976</v>
       </c>
       <c r="K122">
-        <v>1357</v>
+        <v>955</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="N122">
-        <v>145416.8103652774</v>
+        <v>189096.9567127897</v>
       </c>
       <c r="P122">
         <v>0.2</v>
       </c>
       <c r="Q122">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -6676,48 +6679,48 @@
         </is>
       </c>
       <c r="C123">
-        <v>131888</v>
+        <v>102400</v>
       </c>
       <c r="D123">
-        <v>126348.693433955</v>
+        <v>43254.28652665103</v>
       </c>
       <c r="E123">
-        <v>177578.3595131705</v>
+        <v>114921.7067697761</v>
       </c>
       <c r="F123">
-        <v>45690.35951317049</v>
+        <v>12521.70676977609</v>
       </c>
       <c r="G123">
-        <v>0.03777067312196213</v>
+        <v>0.481790396233426</v>
       </c>
       <c r="H123">
-        <v>0.5951812152706798</v>
+        <v>0.05911150543870575</v>
       </c>
       <c r="I123">
-        <v>0.3566478338483174</v>
+        <v>0.395388677510043</v>
       </c>
       <c r="J123">
-        <v>0.01040027775904059</v>
+        <v>0.0637094208178252</v>
       </c>
       <c r="K123">
-        <v>1129</v>
+        <v>702</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="N123">
-        <v>326804.0013846449</v>
+        <v>386548.9231194458</v>
       </c>
       <c r="P123">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="Q123">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -6725,40 +6728,40 @@
         </is>
       </c>
       <c r="C124">
-        <v>274014.0000000001</v>
+        <v>255498</v>
       </c>
       <c r="D124">
-        <v>142359.7940300549</v>
+        <v>207716.095873672</v>
       </c>
       <c r="E124">
-        <v>349334.4500167556</v>
+        <v>289309.9562418167</v>
       </c>
       <c r="F124">
-        <v>75320.45001675549</v>
+        <v>33811.95624181666</v>
       </c>
       <c r="G124">
-        <v>0.3828230960484398</v>
+        <v>0.1432793974269345</v>
       </c>
       <c r="H124">
-        <v>0.2785295642308362</v>
+        <v>0.6826944427680578</v>
       </c>
       <c r="I124">
-        <v>0.3274677149138821</v>
+        <v>0.1699049949987613</v>
       </c>
       <c r="J124">
-        <v>0.01117962480684187</v>
+        <v>0.004121164806246279</v>
       </c>
       <c r="K124">
-        <v>958</v>
+        <v>1357</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="N124">
-        <v>732603.6241928141</v>
+        <v>145416.8103652774</v>
       </c>
       <c r="P124">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="Q124">
         <v>0.1</v>
@@ -6766,7 +6769,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -6774,37 +6777,37 @@
         </is>
       </c>
       <c r="C125">
-        <v>169635.9344258063</v>
+        <v>131888</v>
       </c>
       <c r="D125">
-        <v>162775.9967020668</v>
+        <v>126348.693433955</v>
       </c>
       <c r="E125">
-        <v>225547.1417344348</v>
+        <v>177578.3595131705</v>
       </c>
       <c r="F125">
-        <v>55911.20730862854</v>
+        <v>45690.35951317049</v>
       </c>
       <c r="G125">
-        <v>0.03049579895053175</v>
+        <v>0.03777067312196213</v>
       </c>
       <c r="H125">
-        <v>0.6164675132099063</v>
+        <v>0.5951812152706798</v>
       </c>
       <c r="I125">
-        <v>0.3424457001470055</v>
+        <v>0.3566478338483174</v>
       </c>
       <c r="J125">
-        <v>0.01059098769255645</v>
+        <v>0.01040027775904059</v>
       </c>
       <c r="K125">
-        <v>2694</v>
+        <v>1129</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="N125">
-        <v>353959.4130974241</v>
+        <v>326804.0013846449</v>
       </c>
       <c r="P125">
         <v>0.15</v>
@@ -6815,7 +6818,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -6823,37 +6826,37 @@
         </is>
       </c>
       <c r="C126">
-        <v>126339</v>
+        <v>274014.0000000001</v>
       </c>
       <c r="D126">
-        <v>108568.4424555644</v>
+        <v>142359.7940300549</v>
       </c>
       <c r="E126">
-        <v>194135.5247214137</v>
+        <v>349334.4500167556</v>
       </c>
       <c r="F126">
-        <v>67796.52472141365</v>
+        <v>75320.45001675549</v>
       </c>
       <c r="G126">
-        <v>0.07733418659702468</v>
+        <v>0.3828230960484398</v>
       </c>
       <c r="H126">
-        <v>0.3172407396536939</v>
+        <v>0.2785295642308362</v>
       </c>
       <c r="I126">
-        <v>0.5649786817148452</v>
+        <v>0.3274677149138821</v>
       </c>
       <c r="J126">
-        <v>0.04044639203443616</v>
+        <v>0.01117962480684187</v>
       </c>
       <c r="K126">
-        <v>1056</v>
+        <v>958</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="N126">
-        <v>219482.3284506314</v>
+        <v>732603.6241928141</v>
       </c>
       <c r="P126">
         <v>0.15</v>
@@ -6864,7 +6867,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -6872,37 +6875,37 @@
         </is>
       </c>
       <c r="C127">
-        <v>371518</v>
+        <v>169635.9344258063</v>
       </c>
       <c r="D127">
-        <v>158923.4835797619</v>
+        <v>162775.9967020668</v>
       </c>
       <c r="E127">
-        <v>489390.9382126621</v>
+        <v>225547.1417344348</v>
       </c>
       <c r="F127">
-        <v>117872.9382126621</v>
+        <v>55911.20730862854</v>
       </c>
       <c r="G127">
-        <v>0.440996781448181</v>
+        <v>0.03049579895053175</v>
       </c>
       <c r="H127">
-        <v>0.3962218854835434</v>
+        <v>0.6164675132099063</v>
       </c>
       <c r="I127">
-        <v>0.154422557536307</v>
+        <v>0.3424457001470055</v>
       </c>
       <c r="J127">
-        <v>0.008358775531968548</v>
+        <v>0.01059098769255645</v>
       </c>
       <c r="K127">
-        <v>1860</v>
+        <v>2694</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="N127">
-        <v>150478.2895093822</v>
+        <v>353959.4130974241</v>
       </c>
       <c r="P127">
         <v>0.15</v>
@@ -6913,7 +6916,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -6921,37 +6924,37 @@
         </is>
       </c>
       <c r="C128">
-        <v>220189.0000000001</v>
+        <v>126339</v>
       </c>
       <c r="D128">
-        <v>190971.2796305801</v>
+        <v>108568.4424555644</v>
       </c>
       <c r="E128">
-        <v>432141.3903106273</v>
+        <v>194135.5247214137</v>
       </c>
       <c r="F128">
-        <v>211952.3903106271</v>
+        <v>67796.52472141365</v>
       </c>
       <c r="G128">
-        <v>0.06453931250562381</v>
+        <v>0.07733418659702468</v>
       </c>
       <c r="H128">
-        <v>0.6713044863287302</v>
+        <v>0.3172407396536939</v>
       </c>
       <c r="I128">
-        <v>0.2609677254991165</v>
+        <v>0.5649786817148452</v>
       </c>
       <c r="J128">
-        <v>0.003188475666529429</v>
+        <v>0.04044639203443616</v>
       </c>
       <c r="K128">
-        <v>1979</v>
+        <v>1056</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="N128">
-        <v>131772.1820819404</v>
+        <v>219482.3284506314</v>
       </c>
       <c r="P128">
         <v>0.15</v>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -6970,48 +6973,48 @@
         </is>
       </c>
       <c r="C129">
-        <v>188907.9999999999</v>
+        <v>371518</v>
       </c>
       <c r="D129">
-        <v>163806.536519134</v>
+        <v>158923.4835797619</v>
       </c>
       <c r="E129">
-        <v>443395.7055776317</v>
+        <v>489390.9382126621</v>
       </c>
       <c r="F129">
-        <v>254487.7055776318</v>
+        <v>117872.9382126621</v>
       </c>
       <c r="G129">
-        <v>0.0573970813226258</v>
+        <v>0.440996781448181</v>
       </c>
       <c r="H129">
-        <v>0.4303946106917457</v>
+        <v>0.3962218854835434</v>
       </c>
       <c r="I129">
-        <v>0.5006873743683274</v>
+        <v>0.154422557536307</v>
       </c>
       <c r="J129">
-        <v>0.01152093361730092</v>
+        <v>0.008358775531968548</v>
       </c>
       <c r="K129">
-        <v>1904</v>
+        <v>1860</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
       <c r="N129">
-        <v>21882.51302978364</v>
+        <v>150478.2895093822</v>
       </c>
       <c r="P129">
         <v>0.15</v>
       </c>
       <c r="Q129">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7019,48 +7022,48 @@
         </is>
       </c>
       <c r="C130">
-        <v>150443</v>
+        <v>220189.0000000001</v>
       </c>
       <c r="D130">
-        <v>113797.5141178104</v>
+        <v>190971.2796305801</v>
       </c>
       <c r="E130">
-        <v>282481.4811496572</v>
+        <v>432141.3903106273</v>
       </c>
       <c r="F130">
-        <v>132038.4811496572</v>
+        <v>211952.3903106271</v>
       </c>
       <c r="G130">
-        <v>0.132510253824683</v>
+        <v>0.06453931250562381</v>
       </c>
       <c r="H130">
-        <v>0.3758640108409666</v>
+        <v>0.6713044863287302</v>
       </c>
       <c r="I130">
-        <v>0.4750486844198933</v>
+        <v>0.2609677254991165</v>
       </c>
       <c r="J130">
-        <v>0.01657705091445719</v>
+        <v>0.003188475666529429</v>
       </c>
       <c r="K130">
-        <v>1160</v>
+        <v>1979</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="N130">
-        <v>114009.339885825</v>
+        <v>131772.1820819404</v>
       </c>
       <c r="P130">
         <v>0.15</v>
       </c>
       <c r="Q130">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -7068,48 +7071,48 @@
         </is>
       </c>
       <c r="C131">
-        <v>151138.9997128722</v>
+        <v>188907.9999999999</v>
       </c>
       <c r="D131">
-        <v>131949.3910043361</v>
+        <v>163806.536519134</v>
       </c>
       <c r="E131">
-        <v>192876.4649786821</v>
+        <v>443395.7055776317</v>
       </c>
       <c r="F131">
-        <v>41737.46526580994</v>
+        <v>254487.7055776318</v>
       </c>
       <c r="G131">
-        <v>0.09577870332277878</v>
+        <v>0.0573970813226258</v>
       </c>
       <c r="H131">
-        <v>0.4528421691815802</v>
+        <v>0.4303946106917457</v>
       </c>
       <c r="I131">
-        <v>0.4459781223286151</v>
+        <v>0.5006873743683274</v>
       </c>
       <c r="J131">
-        <v>0.005401005167025924</v>
+        <v>0.01152093361730092</v>
       </c>
       <c r="K131">
-        <v>1263</v>
+        <v>1904</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="N131">
-        <v>333891.8889857767</v>
+        <v>21882.51302978364</v>
       </c>
       <c r="P131">
         <v>0.15</v>
       </c>
       <c r="Q131">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -7117,37 +7120,37 @@
         </is>
       </c>
       <c r="C132">
-        <v>63788.99999999998</v>
+        <v>150443</v>
       </c>
       <c r="D132">
-        <v>61940.19361386459</v>
+        <v>113797.5141178104</v>
       </c>
       <c r="E132">
-        <v>92704.71794149016</v>
+        <v>282481.4811496572</v>
       </c>
       <c r="F132">
-        <v>28915.71794149018</v>
+        <v>132038.4811496572</v>
       </c>
       <c r="G132">
-        <v>0.01878546325598736</v>
+        <v>0.132510253824683</v>
       </c>
       <c r="H132">
-        <v>0.6934973902979632</v>
+        <v>0.3758640108409666</v>
       </c>
       <c r="I132">
-        <v>0.2678756223623517</v>
+        <v>0.4750486844198933</v>
       </c>
       <c r="J132">
-        <v>0.01984152408369781</v>
+        <v>0.01657705091445719</v>
       </c>
       <c r="K132">
-        <v>600</v>
+        <v>1160</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="N132">
-        <v>885638.3882038471</v>
+        <v>114009.339885825</v>
       </c>
       <c r="P132">
         <v>0.15</v>
@@ -7158,7 +7161,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -7166,37 +7169,37 @@
         </is>
       </c>
       <c r="C133">
-        <v>72693</v>
+        <v>151138.9997128722</v>
       </c>
       <c r="D133">
-        <v>52837.04901396133</v>
+        <v>131949.3910043361</v>
       </c>
       <c r="E133">
-        <v>77448.69584715727</v>
+        <v>192876.4649786821</v>
       </c>
       <c r="F133">
-        <v>4755.695847157273</v>
+        <v>41737.46526580994</v>
       </c>
       <c r="G133">
-        <v>0.2493321776238968</v>
+        <v>0.09577870332277878</v>
       </c>
       <c r="H133">
-        <v>0.1155396216309735</v>
+        <v>0.4528421691815802</v>
       </c>
       <c r="I133">
-        <v>0.6238863595182296</v>
+        <v>0.4459781223286151</v>
       </c>
       <c r="J133">
-        <v>0.01124184122690025</v>
+        <v>0.005401005167025924</v>
       </c>
       <c r="K133">
-        <v>643</v>
+        <v>1263</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="N133">
-        <v>811357.3188160737</v>
+        <v>333891.8889857767</v>
       </c>
       <c r="P133">
         <v>0.15</v>
@@ -7207,7 +7210,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -7215,40 +7218,40 @@
         </is>
       </c>
       <c r="C134">
-        <v>116844</v>
+        <v>63788.99999999998</v>
       </c>
       <c r="D134">
-        <v>65332.57981771554</v>
+        <v>61940.19361386459</v>
       </c>
       <c r="E134">
-        <v>116844</v>
+        <v>92704.71794149016</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>28915.71794149018</v>
       </c>
       <c r="G134">
-        <v>0.4201815750193439</v>
+        <v>0.01878546325598736</v>
       </c>
       <c r="H134">
-        <v>0.4816223343431587</v>
+        <v>0.6934973902979632</v>
       </c>
       <c r="I134">
-        <v>0.09229883016583382</v>
+        <v>0.2678756223623517</v>
       </c>
       <c r="J134">
-        <v>0.005897260471663509</v>
+        <v>0.01984152408369781</v>
       </c>
       <c r="K134">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="N134">
-        <v>271240.703074521</v>
+        <v>885638.3882038471</v>
       </c>
       <c r="P134">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="Q134">
         <v>0.07000000000000001</v>
@@ -7256,7 +7259,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -7264,40 +7267,40 @@
         </is>
       </c>
       <c r="C135">
-        <v>177831.0000000001</v>
+        <v>72693</v>
       </c>
       <c r="D135">
-        <v>130289.2303333466</v>
+        <v>52837.04901396133</v>
       </c>
       <c r="E135">
-        <v>240712.4482929232</v>
+        <v>77448.69584715727</v>
       </c>
       <c r="F135">
-        <v>62881.44829292319</v>
+        <v>4755.695847157273</v>
       </c>
       <c r="G135">
-        <v>0.1672982324423302</v>
+        <v>0.2493321776238968</v>
       </c>
       <c r="H135">
-        <v>0.6718166357965669</v>
+        <v>0.1155396216309735</v>
       </c>
       <c r="I135">
-        <v>0.1591899372074296</v>
+        <v>0.6238863595182296</v>
       </c>
       <c r="J135">
-        <v>0.001695194553673259</v>
+        <v>0.01124184122690025</v>
       </c>
       <c r="K135">
-        <v>999</v>
+        <v>643</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="N135">
-        <v>304274.706182281</v>
+        <v>811357.3188160737</v>
       </c>
       <c r="P135">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="Q135">
         <v>0.07000000000000001</v>
@@ -7305,7 +7308,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -7313,48 +7316,48 @@
         </is>
       </c>
       <c r="C136">
-        <v>456436.0000000001</v>
+        <v>116844</v>
       </c>
       <c r="D136">
-        <v>296956.4619695917</v>
+        <v>65332.57981771554</v>
       </c>
       <c r="E136">
-        <v>897995.6407605257</v>
+        <v>116844</v>
       </c>
       <c r="F136">
-        <v>441559.6407605257</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>0.1898784300571245</v>
+        <v>0.4201815750193439</v>
       </c>
       <c r="H136">
-        <v>0.7009058361292453</v>
+        <v>0.4816223343431587</v>
       </c>
       <c r="I136">
-        <v>0.1090985747445236</v>
+        <v>0.09229883016583382</v>
       </c>
       <c r="J136">
-        <v>0.0001171590691066505</v>
+        <v>0.005897260471663509</v>
       </c>
       <c r="K136">
-        <v>2362</v>
+        <v>621</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="N136">
-        <v>1046784.042950014</v>
+        <v>271240.703074521</v>
       </c>
       <c r="P136">
         <v>0.2</v>
       </c>
       <c r="Q136">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -7362,48 +7365,48 @@
         </is>
       </c>
       <c r="C137">
-        <v>439213.9999999999</v>
+        <v>177831.0000000001</v>
       </c>
       <c r="D137">
-        <v>381979.5120743748</v>
+        <v>130289.2303333466</v>
       </c>
       <c r="E137">
-        <v>701818.5778045077</v>
+        <v>240712.4482929232</v>
       </c>
       <c r="F137">
-        <v>262604.5778045078</v>
+        <v>62881.44829292319</v>
       </c>
       <c r="G137">
-        <v>0.07462218912451547</v>
+        <v>0.1672982324423302</v>
       </c>
       <c r="H137">
-        <v>0.5951200081227718</v>
+        <v>0.6718166357965669</v>
       </c>
       <c r="I137">
-        <v>0.2944771578850644</v>
+        <v>0.1591899372074296</v>
       </c>
       <c r="J137">
-        <v>0.03578064486764836</v>
+        <v>0.001695194553673259</v>
       </c>
       <c r="K137">
-        <v>1585</v>
+        <v>999</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="N137">
-        <v>1456288.889933172</v>
+        <v>304274.706182281</v>
       </c>
       <c r="P137">
+        <v>0.2</v>
+      </c>
+      <c r="Q137">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="Q137">
-        <v>0.05</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -7411,40 +7414,40 @@
         </is>
       </c>
       <c r="C138">
-        <v>229381</v>
+        <v>456436.0000000001</v>
       </c>
       <c r="D138">
-        <v>192226.153255183</v>
+        <v>296956.4619695917</v>
       </c>
       <c r="E138">
-        <v>427514.6422917357</v>
+        <v>897995.6407605257</v>
       </c>
       <c r="F138">
-        <v>198133.6422917358</v>
+        <v>441559.6407605257</v>
       </c>
       <c r="G138">
-        <v>0.08153667387830939</v>
+        <v>0.1898784300571245</v>
       </c>
       <c r="H138">
-        <v>0.3876083796957694</v>
+        <v>0.7009058361292453</v>
       </c>
       <c r="I138">
-        <v>0.5091300869981726</v>
+        <v>0.1090985747445236</v>
       </c>
       <c r="J138">
-        <v>0.02172485942774853</v>
+        <v>0.0001171590691066505</v>
       </c>
       <c r="K138">
-        <v>1773</v>
+        <v>2362</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="N138">
-        <v>265560.8989697707</v>
+        <v>1046784.042950014</v>
       </c>
       <c r="P138">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Q138">
         <v>0.05</v>
@@ -7452,7 +7455,7 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -7460,37 +7463,37 @@
         </is>
       </c>
       <c r="C139">
-        <v>467725.0864587884</v>
+        <v>439213.9999999999</v>
       </c>
       <c r="D139">
-        <v>119848.9748692562</v>
+        <v>381979.5120743748</v>
       </c>
       <c r="E139">
-        <v>529426.8763129682</v>
+        <v>701818.5778045077</v>
       </c>
       <c r="F139">
-        <v>61701.78985417978</v>
+        <v>262604.5778045078</v>
       </c>
       <c r="G139">
-        <v>0.6659880991336868</v>
+        <v>0.07462218912451547</v>
       </c>
       <c r="H139">
-        <v>0.2253158795456554</v>
+        <v>0.5951200081227718</v>
       </c>
       <c r="I139">
-        <v>0.09826876148440936</v>
+        <v>0.2944771578850644</v>
       </c>
       <c r="J139">
-        <v>0.01042725983624852</v>
+        <v>0.03578064486764836</v>
       </c>
       <c r="K139">
-        <v>1823</v>
+        <v>1585</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="N139">
-        <v>74647.11735710694</v>
+        <v>1456288.889933172</v>
       </c>
       <c r="P139">
         <v>0.07000000000000001</v>
@@ -7501,7 +7504,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -7509,37 +7512,37 @@
         </is>
       </c>
       <c r="C140">
-        <v>365429.0904846364</v>
+        <v>229381</v>
       </c>
       <c r="D140">
-        <v>159750.6359031179</v>
+        <v>192226.153255183</v>
       </c>
       <c r="E140">
-        <v>828511.1765858305</v>
+        <v>427514.6422917357</v>
       </c>
       <c r="F140">
-        <v>463082.0861011941</v>
+        <v>198133.6422917358</v>
       </c>
       <c r="G140">
-        <v>0.2723610059479785</v>
+        <v>0.08153667387830939</v>
       </c>
       <c r="H140">
-        <v>0.5479348580845913</v>
+        <v>0.3876083796957694</v>
       </c>
       <c r="I140">
-        <v>0.1783341083373614</v>
+        <v>0.5091300869981726</v>
       </c>
       <c r="J140">
-        <v>0.001370027630068778</v>
+        <v>0.02172485942774853</v>
       </c>
       <c r="K140">
-        <v>3241</v>
+        <v>1773</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>421399.4024497316</v>
+        <v>265560.8989697707</v>
       </c>
       <c r="P140">
         <v>0.07000000000000001</v>
@@ -7550,7 +7553,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -7558,37 +7561,37 @@
         </is>
       </c>
       <c r="C141">
-        <v>330247.5699999999</v>
+        <v>467725.0864587884</v>
       </c>
       <c r="D141">
-        <v>312265.2799999999</v>
+        <v>119848.9748692562</v>
       </c>
       <c r="E141">
-        <v>1058331.57</v>
+        <v>529426.8763129682</v>
       </c>
       <c r="F141">
-        <v>728084</v>
+        <v>61701.78985417978</v>
       </c>
       <c r="G141">
-        <v>0.01576952863647447</v>
+        <v>0.6659880991336868</v>
       </c>
       <c r="H141">
-        <v>0.7639572445145901</v>
+        <v>0.2253158795456554</v>
       </c>
       <c r="I141">
-        <v>0.2180277112965647</v>
+        <v>0.09826876148440936</v>
       </c>
       <c r="J141">
-        <v>0.002245515552370795</v>
+        <v>0.01042725983624852</v>
       </c>
       <c r="K141">
-        <v>3100</v>
+        <v>1823</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>103582.4907797132</v>
+        <v>74647.11735710694</v>
       </c>
       <c r="P141">
         <v>0.07000000000000001</v>
@@ -7599,7 +7602,7 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -7607,37 +7610,37 @@
         </is>
       </c>
       <c r="C142">
-        <v>233152.75</v>
+        <v>365429.0904846364</v>
       </c>
       <c r="D142">
-        <v>211925.58</v>
+        <v>159750.6359031179</v>
       </c>
       <c r="E142">
-        <v>525568.75</v>
+        <v>828511.1765858305</v>
       </c>
       <c r="F142">
-        <v>292416</v>
+        <v>463082.0861011941</v>
       </c>
       <c r="G142">
-        <v>0.03741341166117661</v>
+        <v>0.2723610059479785</v>
       </c>
       <c r="H142">
-        <v>0.1585412755229454</v>
+        <v>0.5479348580845913</v>
       </c>
       <c r="I142">
-        <v>0.7860147887407689</v>
+        <v>0.1783341083373614</v>
       </c>
       <c r="J142">
-        <v>0.01803052407510911</v>
+        <v>0.001370027630068778</v>
       </c>
       <c r="K142">
-        <v>2016</v>
+        <v>3241</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="N142">
-        <v>293354.5109088812</v>
+        <v>421399.4024497316</v>
       </c>
       <c r="P142">
         <v>0.07000000000000001</v>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -7656,40 +7659,40 @@
         </is>
       </c>
       <c r="C143">
-        <v>296471.6800000002</v>
+        <v>330247.5699999999</v>
       </c>
       <c r="D143">
-        <v>142683.8700000001</v>
+        <v>312265.2799999999</v>
       </c>
       <c r="E143">
-        <v>354590.2950084583</v>
+        <v>1058331.57</v>
       </c>
       <c r="F143">
-        <v>58118.61500845803</v>
+        <v>728084</v>
       </c>
       <c r="G143">
-        <v>0.4245157973256068</v>
+        <v>0.01576952863647447</v>
       </c>
       <c r="H143">
-        <v>0.09770699925869245</v>
+        <v>0.7639572445145901</v>
       </c>
       <c r="I143">
-        <v>0.4523679562762732</v>
+        <v>0.2180277112965647</v>
       </c>
       <c r="J143">
-        <v>0.02540924713942761</v>
+        <v>0.002245515552370795</v>
       </c>
       <c r="K143">
-        <v>2250</v>
+        <v>3100</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="N143">
-        <v>132750.731163154</v>
+        <v>103582.4907797132</v>
       </c>
       <c r="P143">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q143">
         <v>0.05</v>
@@ -7697,7 +7700,7 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -7705,40 +7708,40 @@
         </is>
       </c>
       <c r="C144">
-        <v>157812.3200000002</v>
+        <v>233152.75</v>
       </c>
       <c r="D144">
-        <v>146311.7000000002</v>
+        <v>211925.58</v>
       </c>
       <c r="E144">
-        <v>224073.6918328513</v>
+        <v>525568.75</v>
       </c>
       <c r="F144">
-        <v>66261.37183285112</v>
+        <v>292416</v>
       </c>
       <c r="G144">
-        <v>0.03795535186090742</v>
+        <v>0.03741341166117661</v>
       </c>
       <c r="H144">
-        <v>0.8575607141314504</v>
+        <v>0.1585412755229454</v>
       </c>
       <c r="I144">
-        <v>0.08153665331915659</v>
+        <v>0.7860147887407689</v>
       </c>
       <c r="J144">
-        <v>0.02294728068848562</v>
+        <v>0.01803052407510911</v>
       </c>
       <c r="K144">
-        <v>1893</v>
+        <v>2016</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="N144">
-        <v>750367.6488816383</v>
+        <v>293354.5109088812</v>
       </c>
       <c r="P144">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q144">
         <v>0.05</v>
@@ -7746,7 +7749,7 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -7754,34 +7757,37 @@
         </is>
       </c>
       <c r="C145">
-        <v>129356.01</v>
+        <v>296471.6800000002</v>
       </c>
       <c r="D145">
-        <v>91244.78999999999</v>
+        <v>142683.8700000001</v>
       </c>
       <c r="E145">
-        <v>169136.38566547</v>
+        <v>354590.2950084583</v>
       </c>
       <c r="F145">
-        <v>39780.37566547004</v>
+        <v>58118.61500845803</v>
       </c>
       <c r="G145">
-        <v>0.2205776644579145</v>
+        <v>0.4245157973256068</v>
       </c>
       <c r="H145">
-        <v>0.3130925929546969</v>
+        <v>0.09770699925869245</v>
       </c>
       <c r="I145">
-        <v>0.4541051421353799</v>
+        <v>0.4523679562762732</v>
       </c>
       <c r="J145">
-        <v>0.01222460045200874</v>
+        <v>0.02540924713942761</v>
       </c>
       <c r="K145">
-        <v>1857</v>
+        <v>2250</v>
       </c>
       <c r="L145">
         <v>0</v>
+      </c>
+      <c r="N145">
+        <v>132750.731163154</v>
       </c>
       <c r="P145">
         <v>0.05</v>
@@ -7792,7 +7798,7 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -7800,34 +7806,37 @@
         </is>
       </c>
       <c r="C146">
-        <v>169445.09</v>
+        <v>157812.3200000002</v>
       </c>
       <c r="D146">
-        <v>131529.48</v>
+        <v>146311.7000000002</v>
       </c>
       <c r="E146">
-        <v>208952.2366804202</v>
+        <v>224073.6918328513</v>
       </c>
       <c r="F146">
-        <v>39507.14668042018</v>
+        <v>66261.37183285112</v>
       </c>
       <c r="G146">
-        <v>0.1930267266991312</v>
+        <v>0.03795535186090742</v>
       </c>
       <c r="H146">
-        <v>0.6639115435558196</v>
+        <v>0.8575607141314504</v>
       </c>
       <c r="I146">
-        <v>0.1339317820045118</v>
+        <v>0.08153665331915659</v>
       </c>
       <c r="J146">
-        <v>0.009129947740537488</v>
+        <v>0.02294728068848562</v>
       </c>
       <c r="K146">
-        <v>1032</v>
+        <v>1893</v>
       </c>
       <c r="L146">
         <v>0</v>
+      </c>
+      <c r="N146">
+        <v>750367.6488816383</v>
       </c>
       <c r="P146">
         <v>0.05</v>
@@ -7838,7 +7847,7 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -7846,34 +7855,37 @@
         </is>
       </c>
       <c r="C147">
-        <v>182340</v>
+        <v>129356.01</v>
       </c>
       <c r="D147">
-        <v>105441</v>
+        <v>91244.78999999999</v>
       </c>
       <c r="E147">
-        <v>251468</v>
+        <v>169136.38566547</v>
       </c>
       <c r="F147">
-        <v>69128</v>
+        <v>39780.37566547004</v>
       </c>
       <c r="G147">
-        <v>0.3011556142332225</v>
+        <v>0.2205776644579145</v>
       </c>
       <c r="H147">
-        <v>0.1982598183466684</v>
+        <v>0.3130925929546969</v>
       </c>
       <c r="I147">
-        <v>0.4443666788617239</v>
+        <v>0.4541051421353799</v>
       </c>
       <c r="J147">
-        <v>0.05621788855838517</v>
+        <v>0.01222460045200874</v>
       </c>
       <c r="K147">
-        <v>1662</v>
+        <v>1857</v>
       </c>
       <c r="L147">
         <v>0</v>
+      </c>
+      <c r="N147">
+        <v>261885.1971519575</v>
       </c>
       <c r="P147">
         <v>0.05</v>
@@ -7884,7 +7896,7 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -7892,31 +7904,31 @@
         </is>
       </c>
       <c r="C148">
-        <v>415241</v>
+        <v>169445.09</v>
       </c>
       <c r="D148">
-        <v>368156</v>
+        <v>131529.48</v>
       </c>
       <c r="E148">
-        <v>649187</v>
+        <v>208952.2366804202</v>
       </c>
       <c r="F148">
-        <v>233946</v>
+        <v>39507.14668042018</v>
       </c>
       <c r="G148">
-        <v>0.08957049355578593</v>
+        <v>0.1930267266991312</v>
       </c>
       <c r="H148">
-        <v>0.8466712981005473</v>
+        <v>0.6639115435558196</v>
       </c>
       <c r="I148">
-        <v>0.0551674633041019</v>
+        <v>0.1339317820045118</v>
       </c>
       <c r="J148">
-        <v>0.008590745039564871</v>
+        <v>0.009129947740537488</v>
       </c>
       <c r="K148">
-        <v>1688</v>
+        <v>1032</v>
       </c>
       <c r="L148">
         <v>0</v>
@@ -7930,7 +7942,7 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -7938,31 +7950,31 @@
         </is>
       </c>
       <c r="C149">
-        <v>155018</v>
+        <v>182340</v>
       </c>
       <c r="D149">
-        <v>122621.6560924115</v>
+        <v>105441</v>
       </c>
       <c r="E149">
-        <v>333723.2566479851</v>
+        <v>251468</v>
       </c>
       <c r="F149">
-        <v>178705.2566479851</v>
+        <v>69128</v>
       </c>
       <c r="G149">
-        <v>0.1032393015245631</v>
+        <v>0.3011556142332225</v>
       </c>
       <c r="H149">
-        <v>0.5033796653180044</v>
+        <v>0.1982598183466684</v>
       </c>
       <c r="I149">
-        <v>0.3731625894443905</v>
+        <v>0.4443666788617239</v>
       </c>
       <c r="J149">
-        <v>0.02021844371304198</v>
+        <v>0.05621788855838517</v>
       </c>
       <c r="K149">
-        <v>2569</v>
+        <v>1662</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -7976,7 +7988,7 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -7984,31 +7996,31 @@
         </is>
       </c>
       <c r="C150">
-        <v>119995</v>
+        <v>415241</v>
       </c>
       <c r="D150">
-        <v>77872.43072344859</v>
+        <v>368156</v>
       </c>
       <c r="E150">
-        <v>193762.6957705026</v>
+        <v>649187</v>
       </c>
       <c r="F150">
-        <v>73767.6957705026</v>
+        <v>233946</v>
       </c>
       <c r="G150">
-        <v>0.2248210820698492</v>
+        <v>0.08957049355578593</v>
       </c>
       <c r="H150">
-        <v>0.5949981558598678</v>
+        <v>0.8466712981005473</v>
       </c>
       <c r="I150">
-        <v>0.1778293586112761</v>
+        <v>0.0551674633041019</v>
       </c>
       <c r="J150">
-        <v>0.002351403459006942</v>
+        <v>0.008590745039564871</v>
       </c>
       <c r="K150">
-        <v>1571</v>
+        <v>1688</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -8017,6 +8029,144 @@
         <v>0.05</v>
       </c>
       <c r="Q150">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2023</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>155018</v>
+      </c>
+      <c r="D151">
+        <v>122621.6560924115</v>
+      </c>
+      <c r="E151">
+        <v>333723.2566479851</v>
+      </c>
+      <c r="F151">
+        <v>178705.2566479851</v>
+      </c>
+      <c r="G151">
+        <v>0.1032393015245631</v>
+      </c>
+      <c r="H151">
+        <v>0.5033796653180044</v>
+      </c>
+      <c r="I151">
+        <v>0.3731625894443905</v>
+      </c>
+      <c r="J151">
+        <v>0.02021844371304198</v>
+      </c>
+      <c r="K151">
+        <v>2569</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0.05</v>
+      </c>
+      <c r="Q151">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2024</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>119995</v>
+      </c>
+      <c r="D152">
+        <v>77872.43072344859</v>
+      </c>
+      <c r="E152">
+        <v>193762.6957705026</v>
+      </c>
+      <c r="F152">
+        <v>73767.6957705026</v>
+      </c>
+      <c r="G152">
+        <v>0.2248210820698492</v>
+      </c>
+      <c r="H152">
+        <v>0.5949981558598678</v>
+      </c>
+      <c r="I152">
+        <v>0.1778293586112761</v>
+      </c>
+      <c r="J152">
+        <v>0.002351403459006942</v>
+      </c>
+      <c r="K152">
+        <v>1571</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0.05</v>
+      </c>
+      <c r="Q152">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2025</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>106313</v>
+      </c>
+      <c r="D153">
+        <v>58924</v>
+      </c>
+      <c r="E153">
+        <v>161878</v>
+      </c>
+      <c r="F153">
+        <v>55565</v>
+      </c>
+      <c r="G153">
+        <v>0.2985952383894044</v>
+      </c>
+      <c r="H153">
+        <v>0.4547931158032593</v>
+      </c>
+      <c r="I153">
+        <v>0.2386365040339021</v>
+      </c>
+      <c r="J153">
+        <v>0.007975141773434315</v>
+      </c>
+      <c r="K153">
+        <v>1353</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0.05</v>
+      </c>
+      <c r="Q153">
         <v>0.05</v>
       </c>
     </row>

--- a/3. outputs/Stock-recruit data/Barkley_Sockeye_stock-recruit_infilled.xlsx
+++ b/3. outputs/Stock-recruit data/Barkley_Sockeye_stock-recruit_infilled.xlsx
@@ -3021,22 +3021,22 @@
         <v>347988</v>
       </c>
       <c r="E50">
-        <v>681226</v>
+        <v>680768</v>
       </c>
       <c r="F50">
-        <v>233609</v>
+        <v>233151</v>
       </c>
       <c r="G50">
-        <v>0.1422831776825899</v>
+        <v>0.142358336467049</v>
       </c>
       <c r="H50">
-        <v>0.5630334132872203</v>
+        <v>0.5629113001786218</v>
       </c>
       <c r="I50">
-        <v>0.289163948528095</v>
+        <v>0.2892071895271223</v>
       </c>
       <c r="J50">
-        <v>0.005519460502094752</v>
+        <v>0.005523173827206919</v>
       </c>
       <c r="K50">
         <v>3262</v>
@@ -4691,7 +4691,7 @@
         <v>783000</v>
       </c>
       <c r="N82">
-        <v>4463.788101820499</v>
+        <v>4463.540619397062</v>
       </c>
       <c r="P82">
         <v>0.15</v>
@@ -4728,7 +4728,7 @@
         <v>755300</v>
       </c>
       <c r="N83">
-        <v>24913.27279902591</v>
+        <v>24897.55884362545</v>
       </c>
       <c r="P83">
         <v>0.15</v>
@@ -4765,7 +4765,7 @@
         <v>97750</v>
       </c>
       <c r="N84">
-        <v>26368.81550920557</v>
+        <v>26342.99362609741</v>
       </c>
       <c r="P84">
         <v>0.15</v>
@@ -4802,7 +4802,7 @@
         <v>1558240</v>
       </c>
       <c r="N85">
-        <v>76368.20998018688</v>
+        <v>76307.31105271897</v>
       </c>
       <c r="P85">
         <v>0.15</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="N86">
-        <v>14327.56678138281</v>
+        <v>14326.88337250361</v>
       </c>
       <c r="P86">
         <v>0.15</v>
@@ -4931,10 +4931,10 @@
         <v>29362.37623762376</v>
       </c>
       <c r="E88">
-        <v>36965.52915932841</v>
+        <v>36929.82098108979</v>
       </c>
       <c r="F88">
-        <v>6965.529159328415</v>
+        <v>6929.820981089788</v>
       </c>
       <c r="G88">
         <v>0.02125412541254126</v>
@@ -4961,10 +4961,10 @@
         <v>34386.77385321101</v>
       </c>
       <c r="O88">
-        <v>0.1884330974759124</v>
+        <v>0.1876483773002382</v>
       </c>
       <c r="P88">
-        <v>0.4362144414764024</v>
+        <v>0.4380345893936605</v>
       </c>
       <c r="Q88">
         <v>0.5</v>
@@ -4986,10 +4986,10 @@
         <v>29696.9696969697</v>
       </c>
       <c r="E89">
-        <v>58671.61619560767</v>
+        <v>58603.95871656714</v>
       </c>
       <c r="F89">
-        <v>28671.61619560767</v>
+        <v>28603.95871656714</v>
       </c>
       <c r="G89">
         <v>0.0101010101010101</v>
@@ -5016,10 +5016,10 @@
         <v>8643.726146788991</v>
       </c>
       <c r="O89">
-        <v>0.4886795021977614</v>
+        <v>0.4880891895871344</v>
       </c>
       <c r="P89">
-        <v>0.4362144414764024</v>
+        <v>0.4380345893936605</v>
       </c>
       <c r="Q89">
         <v>0.5</v>
@@ -5754,10 +5754,10 @@
         <v>15911.26308229999</v>
       </c>
       <c r="E104">
-        <v>20887</v>
+        <v>20605</v>
       </c>
       <c r="F104">
-        <v>4923</v>
+        <v>4641</v>
       </c>
       <c r="G104">
         <v>0.003303490209221046</v>
@@ -8140,22 +8140,22 @@
         <v>58924</v>
       </c>
       <c r="E153">
-        <v>161878</v>
+        <v>161849</v>
       </c>
       <c r="F153">
-        <v>55565</v>
+        <v>55536</v>
       </c>
       <c r="G153">
-        <v>0.2985952383894044</v>
+        <v>0.2986487404926815</v>
       </c>
       <c r="H153">
-        <v>0.4547931158032593</v>
+        <v>0.4547942835606028</v>
       </c>
       <c r="I153">
-        <v>0.2386365040339021</v>
+        <v>0.2385804051924942</v>
       </c>
       <c r="J153">
-        <v>0.007975141773434315</v>
+        <v>0.007976570754221528</v>
       </c>
       <c r="K153">
         <v>1353</v>
